--- a/backend/templates/pr-template 3p.xlsx
+++ b/backend/templates/pr-template 3p.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\web-opr\backend\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61C6A155-9A9C-4583-9BB4-ECA3B9D826E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27FF9B94-C5AA-4D52-A2C9-F3D5B7E03420}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -124,11 +124,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -211,13 +210,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
@@ -401,12 +393,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="92">
+  <cellXfs count="87">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -511,21 +502,6 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -535,8 +511,8 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -660,12 +636,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="3">
-    <cellStyle name="Comma" xfId="2" builtinId="3"/>
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
   </cellStyles>
@@ -1082,26 +1057,26 @@
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
-      <c r="E1" s="57"/>
-      <c r="F1" s="58"/>
+      <c r="E1" s="52"/>
+      <c r="F1" s="53"/>
     </row>
     <row r="2" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="59" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="60"/>
-      <c r="C2" s="60"/>
-      <c r="D2" s="60"/>
-      <c r="E2" s="60"/>
-      <c r="F2" s="61"/>
+      <c r="A2" s="54" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="55"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="56"/>
     </row>
     <row r="3" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="62"/>
-      <c r="B3" s="63"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="64"/>
+      <c r="A3" s="57"/>
+      <c r="B3" s="58"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="59"/>
     </row>
     <row r="4" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
@@ -1109,846 +1084,846 @@
       </c>
       <c r="B4" s="26"/>
       <c r="C4" s="27"/>
-      <c r="D4" s="65"/>
-      <c r="E4" s="65"/>
-      <c r="F4" s="66"/>
+      <c r="D4" s="60"/>
+      <c r="E4" s="60"/>
+      <c r="F4" s="61"/>
     </row>
     <row r="5" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="67" t="s">
+      <c r="A5" s="62" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="68"/>
+      <c r="B5" s="63"/>
       <c r="C5" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D5" s="5"/>
-      <c r="E5" s="69" t="s">
+      <c r="E5" s="64" t="s">
         <v>18</v>
       </c>
-      <c r="F5" s="70"/>
+      <c r="F5" s="65"/>
     </row>
     <row r="6" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="51"/>
-      <c r="B6" s="52"/>
+      <c r="A6" s="46"/>
+      <c r="B6" s="47"/>
       <c r="C6" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D6" s="7"/>
-      <c r="E6" s="49" t="s">
+      <c r="E6" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="F6" s="50"/>
+      <c r="F6" s="45"/>
     </row>
     <row r="7" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="53" t="s">
+      <c r="A7" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="55" t="s">
+      <c r="B7" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="55" t="s">
+      <c r="C7" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="55" t="s">
+      <c r="D7" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="E7" s="55" t="s">
+      <c r="E7" s="50" t="s">
         <v>7</v>
       </c>
-      <c r="F7" s="55" t="s">
+      <c r="F7" s="50" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="54"/>
-      <c r="B8" s="56"/>
-      <c r="C8" s="56"/>
-      <c r="D8" s="56"/>
-      <c r="E8" s="56"/>
-      <c r="F8" s="56"/>
+      <c r="A8" s="49"/>
+      <c r="B8" s="51"/>
+      <c r="C8" s="51"/>
+      <c r="D8" s="51"/>
+      <c r="E8" s="51"/>
+      <c r="F8" s="51"/>
     </row>
     <row r="9" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="46"/>
-      <c r="B9" s="47"/>
-      <c r="C9" s="45"/>
-      <c r="D9" s="45"/>
-      <c r="E9" s="48"/>
+      <c r="A9" s="41"/>
+      <c r="B9" s="42"/>
+      <c r="C9" s="40"/>
+      <c r="D9" s="40"/>
+      <c r="E9" s="86"/>
       <c r="F9" s="39">
         <f t="shared" ref="F9:F45" si="0">D9*E9</f>
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="46"/>
-      <c r="B10" s="47"/>
-      <c r="C10" s="45"/>
-      <c r="D10" s="45"/>
-      <c r="E10" s="48"/>
+      <c r="A10" s="41"/>
+      <c r="B10" s="42"/>
+      <c r="C10" s="40"/>
+      <c r="D10" s="40"/>
+      <c r="E10" s="86"/>
       <c r="F10" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="46"/>
-      <c r="B11" s="47"/>
-      <c r="C11" s="45"/>
-      <c r="D11" s="45"/>
-      <c r="E11" s="48"/>
+      <c r="A11" s="41"/>
+      <c r="B11" s="42"/>
+      <c r="C11" s="40"/>
+      <c r="D11" s="40"/>
+      <c r="E11" s="86"/>
       <c r="F11" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="46"/>
-      <c r="B12" s="47"/>
-      <c r="C12" s="45"/>
-      <c r="D12" s="45"/>
-      <c r="E12" s="48"/>
+      <c r="A12" s="41"/>
+      <c r="B12" s="42"/>
+      <c r="C12" s="40"/>
+      <c r="D12" s="40"/>
+      <c r="E12" s="86"/>
       <c r="F12" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="46"/>
-      <c r="B13" s="47"/>
-      <c r="C13" s="45"/>
-      <c r="D13" s="45"/>
-      <c r="E13" s="48"/>
+      <c r="A13" s="41"/>
+      <c r="B13" s="42"/>
+      <c r="C13" s="40"/>
+      <c r="D13" s="40"/>
+      <c r="E13" s="86"/>
       <c r="F13" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="46"/>
-      <c r="B14" s="47"/>
-      <c r="C14" s="45"/>
-      <c r="D14" s="45"/>
-      <c r="E14" s="48"/>
+      <c r="A14" s="41"/>
+      <c r="B14" s="42"/>
+      <c r="C14" s="40"/>
+      <c r="D14" s="40"/>
+      <c r="E14" s="86"/>
       <c r="F14" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="46"/>
-      <c r="B15" s="47"/>
-      <c r="C15" s="45"/>
-      <c r="D15" s="45"/>
-      <c r="E15" s="48"/>
+      <c r="A15" s="41"/>
+      <c r="B15" s="42"/>
+      <c r="C15" s="40"/>
+      <c r="D15" s="40"/>
+      <c r="E15" s="86"/>
       <c r="F15" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="46"/>
-      <c r="B16" s="47"/>
-      <c r="C16" s="45"/>
-      <c r="D16" s="45"/>
-      <c r="E16" s="48"/>
+      <c r="A16" s="41"/>
+      <c r="B16" s="42"/>
+      <c r="C16" s="40"/>
+      <c r="D16" s="40"/>
+      <c r="E16" s="86"/>
       <c r="F16" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="46"/>
-      <c r="B17" s="47"/>
-      <c r="C17" s="45"/>
-      <c r="D17" s="45"/>
-      <c r="E17" s="48"/>
+      <c r="A17" s="41"/>
+      <c r="B17" s="42"/>
+      <c r="C17" s="40"/>
+      <c r="D17" s="40"/>
+      <c r="E17" s="86"/>
       <c r="F17" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="46"/>
-      <c r="B18" s="47"/>
-      <c r="C18" s="45"/>
-      <c r="D18" s="45"/>
-      <c r="E18" s="48"/>
+      <c r="A18" s="41"/>
+      <c r="B18" s="42"/>
+      <c r="C18" s="40"/>
+      <c r="D18" s="40"/>
+      <c r="E18" s="86"/>
       <c r="F18" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="46"/>
-      <c r="B19" s="47"/>
-      <c r="C19" s="45"/>
-      <c r="D19" s="45"/>
-      <c r="E19" s="48"/>
+      <c r="A19" s="41"/>
+      <c r="B19" s="42"/>
+      <c r="C19" s="40"/>
+      <c r="D19" s="40"/>
+      <c r="E19" s="86"/>
       <c r="F19" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="46"/>
-      <c r="B20" s="47"/>
-      <c r="C20" s="45"/>
-      <c r="D20" s="45"/>
-      <c r="E20" s="48"/>
+      <c r="A20" s="41"/>
+      <c r="B20" s="42"/>
+      <c r="C20" s="40"/>
+      <c r="D20" s="40"/>
+      <c r="E20" s="86"/>
       <c r="F20" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="46"/>
-      <c r="B21" s="47"/>
-      <c r="C21" s="45"/>
-      <c r="D21" s="45"/>
-      <c r="E21" s="48"/>
+      <c r="A21" s="41"/>
+      <c r="B21" s="42"/>
+      <c r="C21" s="40"/>
+      <c r="D21" s="40"/>
+      <c r="E21" s="86"/>
       <c r="F21" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="46"/>
-      <c r="B22" s="47"/>
-      <c r="C22" s="45"/>
-      <c r="D22" s="45"/>
-      <c r="E22" s="48"/>
+      <c r="A22" s="41"/>
+      <c r="B22" s="42"/>
+      <c r="C22" s="40"/>
+      <c r="D22" s="40"/>
+      <c r="E22" s="86"/>
       <c r="F22" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="46"/>
-      <c r="B23" s="47"/>
-      <c r="C23" s="45"/>
-      <c r="D23" s="45"/>
-      <c r="E23" s="48"/>
+      <c r="A23" s="41"/>
+      <c r="B23" s="42"/>
+      <c r="C23" s="40"/>
+      <c r="D23" s="40"/>
+      <c r="E23" s="86"/>
       <c r="F23" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="46"/>
-      <c r="B24" s="47"/>
-      <c r="C24" s="45"/>
-      <c r="D24" s="45"/>
-      <c r="E24" s="48"/>
+      <c r="A24" s="41"/>
+      <c r="B24" s="42"/>
+      <c r="C24" s="40"/>
+      <c r="D24" s="40"/>
+      <c r="E24" s="86"/>
       <c r="F24" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="46"/>
-      <c r="B25" s="47"/>
-      <c r="C25" s="45"/>
-      <c r="D25" s="45"/>
-      <c r="E25" s="48"/>
+      <c r="A25" s="41"/>
+      <c r="B25" s="42"/>
+      <c r="C25" s="40"/>
+      <c r="D25" s="40"/>
+      <c r="E25" s="86"/>
       <c r="F25" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="46"/>
-      <c r="B26" s="47"/>
-      <c r="C26" s="45"/>
-      <c r="D26" s="45"/>
-      <c r="E26" s="48"/>
+      <c r="A26" s="41"/>
+      <c r="B26" s="42"/>
+      <c r="C26" s="40"/>
+      <c r="D26" s="40"/>
+      <c r="E26" s="86"/>
       <c r="F26" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="46"/>
-      <c r="B27" s="47"/>
-      <c r="C27" s="45"/>
-      <c r="D27" s="45"/>
-      <c r="E27" s="48"/>
+      <c r="A27" s="41"/>
+      <c r="B27" s="42"/>
+      <c r="C27" s="40"/>
+      <c r="D27" s="40"/>
+      <c r="E27" s="86"/>
       <c r="F27" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="46"/>
-      <c r="B28" s="47"/>
-      <c r="C28" s="45"/>
-      <c r="D28" s="45"/>
-      <c r="E28" s="48"/>
+      <c r="A28" s="41"/>
+      <c r="B28" s="42"/>
+      <c r="C28" s="40"/>
+      <c r="D28" s="40"/>
+      <c r="E28" s="86"/>
       <c r="F28" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="46"/>
-      <c r="B29" s="47"/>
-      <c r="C29" s="45"/>
-      <c r="D29" s="45"/>
-      <c r="E29" s="48"/>
+      <c r="A29" s="41"/>
+      <c r="B29" s="42"/>
+      <c r="C29" s="40"/>
+      <c r="D29" s="40"/>
+      <c r="E29" s="86"/>
       <c r="F29" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="46"/>
-      <c r="B30" s="47"/>
-      <c r="C30" s="45"/>
-      <c r="D30" s="45"/>
-      <c r="E30" s="48"/>
+      <c r="A30" s="41"/>
+      <c r="B30" s="42"/>
+      <c r="C30" s="40"/>
+      <c r="D30" s="40"/>
+      <c r="E30" s="86"/>
       <c r="F30" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="46"/>
-      <c r="B31" s="47"/>
-      <c r="C31" s="45"/>
-      <c r="D31" s="45"/>
-      <c r="E31" s="48"/>
+      <c r="A31" s="41"/>
+      <c r="B31" s="42"/>
+      <c r="C31" s="40"/>
+      <c r="D31" s="40"/>
+      <c r="E31" s="86"/>
       <c r="F31" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="46"/>
-      <c r="B32" s="47"/>
-      <c r="C32" s="45"/>
-      <c r="D32" s="45"/>
-      <c r="E32" s="48"/>
+      <c r="A32" s="41"/>
+      <c r="B32" s="42"/>
+      <c r="C32" s="40"/>
+      <c r="D32" s="40"/>
+      <c r="E32" s="86"/>
       <c r="F32" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="46"/>
-      <c r="B33" s="47"/>
-      <c r="C33" s="45"/>
-      <c r="D33" s="45"/>
-      <c r="E33" s="48"/>
+      <c r="A33" s="41"/>
+      <c r="B33" s="42"/>
+      <c r="C33" s="40"/>
+      <c r="D33" s="40"/>
+      <c r="E33" s="86"/>
       <c r="F33" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="46"/>
-      <c r="B34" s="47"/>
-      <c r="C34" s="45"/>
-      <c r="D34" s="45"/>
-      <c r="E34" s="48"/>
+      <c r="A34" s="41"/>
+      <c r="B34" s="42"/>
+      <c r="C34" s="40"/>
+      <c r="D34" s="40"/>
+      <c r="E34" s="86"/>
       <c r="F34" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="46"/>
-      <c r="B35" s="47"/>
-      <c r="C35" s="45"/>
-      <c r="D35" s="45"/>
-      <c r="E35" s="48"/>
+      <c r="A35" s="41"/>
+      <c r="B35" s="42"/>
+      <c r="C35" s="40"/>
+      <c r="D35" s="40"/>
+      <c r="E35" s="86"/>
       <c r="F35" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="46"/>
-      <c r="B36" s="47"/>
-      <c r="C36" s="45"/>
-      <c r="D36" s="45"/>
-      <c r="E36" s="48"/>
+      <c r="A36" s="41"/>
+      <c r="B36" s="42"/>
+      <c r="C36" s="40"/>
+      <c r="D36" s="40"/>
+      <c r="E36" s="86"/>
       <c r="F36" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="46"/>
-      <c r="B37" s="47"/>
-      <c r="C37" s="45"/>
-      <c r="D37" s="45"/>
-      <c r="E37" s="48"/>
+      <c r="A37" s="41"/>
+      <c r="B37" s="42"/>
+      <c r="C37" s="40"/>
+      <c r="D37" s="40"/>
+      <c r="E37" s="86"/>
       <c r="F37" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="46"/>
-      <c r="B38" s="47"/>
-      <c r="C38" s="45"/>
-      <c r="D38" s="45"/>
-      <c r="E38" s="48"/>
+      <c r="A38" s="41"/>
+      <c r="B38" s="42"/>
+      <c r="C38" s="40"/>
+      <c r="D38" s="40"/>
+      <c r="E38" s="86"/>
       <c r="F38" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="46"/>
-      <c r="B39" s="47"/>
-      <c r="C39" s="45"/>
-      <c r="D39" s="45"/>
-      <c r="E39" s="48"/>
+      <c r="A39" s="41"/>
+      <c r="B39" s="42"/>
+      <c r="C39" s="40"/>
+      <c r="D39" s="40"/>
+      <c r="E39" s="86"/>
       <c r="F39" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G39" s="91" t="s">
+      <c r="G39" s="43" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="46"/>
-      <c r="B40" s="47"/>
-      <c r="C40" s="45"/>
-      <c r="D40" s="45"/>
-      <c r="E40" s="48"/>
+      <c r="A40" s="41"/>
+      <c r="B40" s="42"/>
+      <c r="C40" s="40"/>
+      <c r="D40" s="40"/>
+      <c r="E40" s="86"/>
       <c r="F40" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G40" s="91" t="s">
+      <c r="G40" s="43" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="46"/>
-      <c r="B41" s="47"/>
-      <c r="C41" s="45"/>
-      <c r="D41" s="45"/>
-      <c r="E41" s="48"/>
+      <c r="A41" s="41"/>
+      <c r="B41" s="42"/>
+      <c r="C41" s="40"/>
+      <c r="D41" s="40"/>
+      <c r="E41" s="86"/>
       <c r="F41" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="46"/>
-      <c r="B42" s="47"/>
-      <c r="C42" s="45"/>
-      <c r="D42" s="45"/>
-      <c r="E42" s="48"/>
+      <c r="A42" s="41"/>
+      <c r="B42" s="42"/>
+      <c r="C42" s="40"/>
+      <c r="D42" s="40"/>
+      <c r="E42" s="86"/>
       <c r="F42" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="46"/>
-      <c r="B43" s="47"/>
-      <c r="C43" s="45"/>
-      <c r="D43" s="45"/>
-      <c r="E43" s="48"/>
+      <c r="A43" s="41"/>
+      <c r="B43" s="42"/>
+      <c r="C43" s="40"/>
+      <c r="D43" s="40"/>
+      <c r="E43" s="86"/>
       <c r="F43" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="46"/>
-      <c r="B44" s="47"/>
-      <c r="C44" s="45"/>
-      <c r="D44" s="45"/>
-      <c r="E44" s="48"/>
+      <c r="A44" s="41"/>
+      <c r="B44" s="42"/>
+      <c r="C44" s="40"/>
+      <c r="D44" s="40"/>
+      <c r="E44" s="86"/>
       <c r="F44" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="46"/>
-      <c r="B45" s="47"/>
-      <c r="C45" s="45"/>
-      <c r="D45" s="45"/>
-      <c r="E45" s="48"/>
+      <c r="A45" s="41"/>
+      <c r="B45" s="42"/>
+      <c r="C45" s="40"/>
+      <c r="D45" s="40"/>
+      <c r="E45" s="86"/>
       <c r="F45" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="46"/>
-      <c r="B46" s="47"/>
-      <c r="C46" s="45"/>
-      <c r="D46" s="45"/>
-      <c r="E46" s="48"/>
+      <c r="A46" s="41"/>
+      <c r="B46" s="42"/>
+      <c r="C46" s="40"/>
+      <c r="D46" s="40"/>
+      <c r="E46" s="86"/>
       <c r="F46" s="39">
         <f t="shared" ref="F46:F79" si="1">D46*E46</f>
         <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="46"/>
-      <c r="B47" s="47"/>
-      <c r="C47" s="45"/>
-      <c r="D47" s="45"/>
-      <c r="E47" s="48"/>
+      <c r="A47" s="41"/>
+      <c r="B47" s="42"/>
+      <c r="C47" s="40"/>
+      <c r="D47" s="40"/>
+      <c r="E47" s="86"/>
       <c r="F47" s="39">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="46"/>
-      <c r="B48" s="47"/>
-      <c r="C48" s="45"/>
-      <c r="D48" s="45"/>
-      <c r="E48" s="48"/>
+      <c r="A48" s="41"/>
+      <c r="B48" s="42"/>
+      <c r="C48" s="40"/>
+      <c r="D48" s="40"/>
+      <c r="E48" s="86"/>
       <c r="F48" s="39">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="46"/>
-      <c r="B49" s="47"/>
-      <c r="C49" s="45"/>
-      <c r="D49" s="45"/>
-      <c r="E49" s="48"/>
+      <c r="A49" s="41"/>
+      <c r="B49" s="42"/>
+      <c r="C49" s="40"/>
+      <c r="D49" s="40"/>
+      <c r="E49" s="86"/>
       <c r="F49" s="39">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="46"/>
-      <c r="B50" s="47"/>
-      <c r="C50" s="45"/>
-      <c r="D50" s="45"/>
-      <c r="E50" s="48"/>
+      <c r="A50" s="41"/>
+      <c r="B50" s="42"/>
+      <c r="C50" s="40"/>
+      <c r="D50" s="40"/>
+      <c r="E50" s="86"/>
       <c r="F50" s="39">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="46"/>
-      <c r="B51" s="47"/>
-      <c r="C51" s="45"/>
-      <c r="D51" s="45"/>
-      <c r="E51" s="48"/>
+      <c r="A51" s="41"/>
+      <c r="B51" s="42"/>
+      <c r="C51" s="40"/>
+      <c r="D51" s="40"/>
+      <c r="E51" s="86"/>
       <c r="F51" s="39">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="46"/>
-      <c r="B52" s="47"/>
-      <c r="C52" s="45"/>
-      <c r="D52" s="45"/>
-      <c r="E52" s="48"/>
+      <c r="A52" s="41"/>
+      <c r="B52" s="42"/>
+      <c r="C52" s="40"/>
+      <c r="D52" s="40"/>
+      <c r="E52" s="86"/>
       <c r="F52" s="39">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="46"/>
-      <c r="B53" s="47"/>
-      <c r="C53" s="45"/>
-      <c r="D53" s="45"/>
-      <c r="E53" s="48"/>
+      <c r="A53" s="41"/>
+      <c r="B53" s="42"/>
+      <c r="C53" s="40"/>
+      <c r="D53" s="40"/>
+      <c r="E53" s="86"/>
       <c r="F53" s="39">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="46"/>
-      <c r="B54" s="47"/>
-      <c r="C54" s="45"/>
-      <c r="D54" s="45"/>
-      <c r="E54" s="48"/>
+      <c r="A54" s="41"/>
+      <c r="B54" s="42"/>
+      <c r="C54" s="40"/>
+      <c r="D54" s="40"/>
+      <c r="E54" s="86"/>
       <c r="F54" s="39">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="46"/>
-      <c r="B55" s="47"/>
-      <c r="C55" s="45"/>
-      <c r="D55" s="45"/>
-      <c r="E55" s="48"/>
+      <c r="A55" s="41"/>
+      <c r="B55" s="42"/>
+      <c r="C55" s="40"/>
+      <c r="D55" s="40"/>
+      <c r="E55" s="86"/>
       <c r="F55" s="39">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="46"/>
-      <c r="B56" s="47"/>
-      <c r="C56" s="45"/>
-      <c r="D56" s="45"/>
-      <c r="E56" s="48"/>
+      <c r="A56" s="41"/>
+      <c r="B56" s="42"/>
+      <c r="C56" s="40"/>
+      <c r="D56" s="40"/>
+      <c r="E56" s="86"/>
       <c r="F56" s="39">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="46"/>
-      <c r="B57" s="47"/>
-      <c r="C57" s="45"/>
-      <c r="D57" s="45"/>
-      <c r="E57" s="48"/>
+      <c r="A57" s="41"/>
+      <c r="B57" s="42"/>
+      <c r="C57" s="40"/>
+      <c r="D57" s="40"/>
+      <c r="E57" s="86"/>
       <c r="F57" s="39">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A58" s="46"/>
-      <c r="B58" s="47"/>
-      <c r="C58" s="45"/>
-      <c r="D58" s="45"/>
-      <c r="E58" s="48"/>
+      <c r="A58" s="41"/>
+      <c r="B58" s="42"/>
+      <c r="C58" s="40"/>
+      <c r="D58" s="40"/>
+      <c r="E58" s="86"/>
       <c r="F58" s="39">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A59" s="46"/>
-      <c r="B59" s="47"/>
-      <c r="C59" s="45"/>
-      <c r="D59" s="45"/>
-      <c r="E59" s="48"/>
+      <c r="A59" s="41"/>
+      <c r="B59" s="42"/>
+      <c r="C59" s="40"/>
+      <c r="D59" s="40"/>
+      <c r="E59" s="86"/>
       <c r="F59" s="39">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="46"/>
-      <c r="B60" s="47"/>
-      <c r="C60" s="45"/>
-      <c r="D60" s="45"/>
-      <c r="E60" s="48"/>
+      <c r="A60" s="41"/>
+      <c r="B60" s="42"/>
+      <c r="C60" s="40"/>
+      <c r="D60" s="40"/>
+      <c r="E60" s="86"/>
       <c r="F60" s="39">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="46"/>
-      <c r="B61" s="47"/>
-      <c r="C61" s="45"/>
-      <c r="D61" s="45"/>
-      <c r="E61" s="48"/>
+      <c r="A61" s="41"/>
+      <c r="B61" s="42"/>
+      <c r="C61" s="40"/>
+      <c r="D61" s="40"/>
+      <c r="E61" s="86"/>
       <c r="F61" s="39">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="46"/>
-      <c r="B62" s="47"/>
-      <c r="C62" s="45"/>
-      <c r="D62" s="45"/>
-      <c r="E62" s="48"/>
+      <c r="A62" s="41"/>
+      <c r="B62" s="42"/>
+      <c r="C62" s="40"/>
+      <c r="D62" s="40"/>
+      <c r="E62" s="86"/>
       <c r="F62" s="39">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="46"/>
-      <c r="B63" s="47"/>
-      <c r="C63" s="45"/>
-      <c r="D63" s="45"/>
-      <c r="E63" s="48"/>
+      <c r="A63" s="41"/>
+      <c r="B63" s="42"/>
+      <c r="C63" s="40"/>
+      <c r="D63" s="40"/>
+      <c r="E63" s="86"/>
       <c r="F63" s="39">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="46"/>
-      <c r="B64" s="47"/>
-      <c r="C64" s="45"/>
-      <c r="D64" s="45"/>
-      <c r="E64" s="48"/>
+      <c r="A64" s="41"/>
+      <c r="B64" s="42"/>
+      <c r="C64" s="40"/>
+      <c r="D64" s="40"/>
+      <c r="E64" s="86"/>
       <c r="F64" s="39">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="46"/>
-      <c r="B65" s="47"/>
-      <c r="C65" s="45"/>
-      <c r="D65" s="45"/>
-      <c r="E65" s="48"/>
+      <c r="A65" s="41"/>
+      <c r="B65" s="42"/>
+      <c r="C65" s="40"/>
+      <c r="D65" s="40"/>
+      <c r="E65" s="86"/>
       <c r="F65" s="39">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A66" s="46"/>
-      <c r="B66" s="47"/>
-      <c r="C66" s="45"/>
-      <c r="D66" s="45"/>
-      <c r="E66" s="48"/>
+      <c r="A66" s="41"/>
+      <c r="B66" s="42"/>
+      <c r="C66" s="40"/>
+      <c r="D66" s="40"/>
+      <c r="E66" s="86"/>
       <c r="F66" s="39">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="67" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A67" s="46"/>
-      <c r="B67" s="47"/>
-      <c r="C67" s="45"/>
-      <c r="D67" s="45"/>
-      <c r="E67" s="48"/>
+      <c r="A67" s="41"/>
+      <c r="B67" s="42"/>
+      <c r="C67" s="40"/>
+      <c r="D67" s="40"/>
+      <c r="E67" s="86"/>
       <c r="F67" s="39">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="68" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="46"/>
-      <c r="B68" s="47"/>
-      <c r="C68" s="45"/>
-      <c r="D68" s="45"/>
-      <c r="E68" s="48"/>
+      <c r="A68" s="41"/>
+      <c r="B68" s="42"/>
+      <c r="C68" s="40"/>
+      <c r="D68" s="40"/>
+      <c r="E68" s="86"/>
       <c r="F68" s="39">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="46"/>
-      <c r="B69" s="47"/>
-      <c r="C69" s="45"/>
-      <c r="D69" s="45"/>
-      <c r="E69" s="48"/>
+      <c r="A69" s="41"/>
+      <c r="B69" s="42"/>
+      <c r="C69" s="40"/>
+      <c r="D69" s="40"/>
+      <c r="E69" s="86"/>
       <c r="F69" s="39">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="46"/>
-      <c r="B70" s="47"/>
-      <c r="C70" s="45"/>
-      <c r="D70" s="45"/>
-      <c r="E70" s="48"/>
+      <c r="A70" s="41"/>
+      <c r="B70" s="42"/>
+      <c r="C70" s="40"/>
+      <c r="D70" s="40"/>
+      <c r="E70" s="86"/>
       <c r="F70" s="39">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="46"/>
-      <c r="B71" s="47"/>
-      <c r="C71" s="45"/>
-      <c r="D71" s="45"/>
-      <c r="E71" s="48"/>
+      <c r="A71" s="41"/>
+      <c r="B71" s="42"/>
+      <c r="C71" s="40"/>
+      <c r="D71" s="40"/>
+      <c r="E71" s="86"/>
       <c r="F71" s="39">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="46"/>
-      <c r="B72" s="47"/>
-      <c r="C72" s="45"/>
-      <c r="D72" s="45"/>
-      <c r="E72" s="48"/>
+      <c r="A72" s="41"/>
+      <c r="B72" s="42"/>
+      <c r="C72" s="40"/>
+      <c r="D72" s="40"/>
+      <c r="E72" s="86"/>
       <c r="F72" s="39">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="46"/>
-      <c r="B73" s="47"/>
-      <c r="C73" s="45"/>
-      <c r="D73" s="45"/>
-      <c r="E73" s="48"/>
+      <c r="A73" s="41"/>
+      <c r="B73" s="42"/>
+      <c r="C73" s="40"/>
+      <c r="D73" s="40"/>
+      <c r="E73" s="86"/>
       <c r="F73" s="39">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A74" s="46"/>
-      <c r="B74" s="47"/>
-      <c r="C74" s="45"/>
-      <c r="D74" s="45"/>
-      <c r="E74" s="48"/>
+      <c r="A74" s="41"/>
+      <c r="B74" s="42"/>
+      <c r="C74" s="40"/>
+      <c r="D74" s="40"/>
+      <c r="E74" s="86"/>
       <c r="F74" s="39">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A75" s="46"/>
-      <c r="B75" s="47"/>
-      <c r="C75" s="45"/>
-      <c r="D75" s="45"/>
-      <c r="E75" s="48"/>
+      <c r="A75" s="41"/>
+      <c r="B75" s="42"/>
+      <c r="C75" s="40"/>
+      <c r="D75" s="40"/>
+      <c r="E75" s="86"/>
       <c r="F75" s="39">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="46"/>
-      <c r="B76" s="47"/>
-      <c r="C76" s="45"/>
-      <c r="D76" s="45"/>
-      <c r="E76" s="48"/>
+      <c r="A76" s="41"/>
+      <c r="B76" s="42"/>
+      <c r="C76" s="40"/>
+      <c r="D76" s="40"/>
+      <c r="E76" s="86"/>
       <c r="F76" s="39">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="77" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="46"/>
-      <c r="B77" s="47"/>
-      <c r="C77" s="45"/>
-      <c r="D77" s="45"/>
-      <c r="E77" s="48"/>
+      <c r="A77" s="41"/>
+      <c r="B77" s="42"/>
+      <c r="C77" s="40"/>
+      <c r="D77" s="40"/>
+      <c r="E77" s="86"/>
       <c r="F77" s="39">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="46"/>
-      <c r="B78" s="47"/>
-      <c r="C78" s="45"/>
-      <c r="D78" s="45"/>
-      <c r="E78" s="48"/>
+      <c r="A78" s="41"/>
+      <c r="B78" s="42"/>
+      <c r="C78" s="40"/>
+      <c r="D78" s="40"/>
+      <c r="E78" s="86"/>
       <c r="F78" s="39">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="79" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="46"/>
-      <c r="B79" s="47"/>
-      <c r="C79" s="45"/>
-      <c r="D79" s="45"/>
-      <c r="E79" s="48"/>
+      <c r="A79" s="41"/>
+      <c r="B79" s="42"/>
+      <c r="C79" s="40"/>
+      <c r="D79" s="40"/>
+      <c r="E79" s="86"/>
       <c r="F79" s="39">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -1959,12 +1934,12 @@
       <c r="B80" s="28"/>
       <c r="C80" s="34"/>
       <c r="D80" s="29"/>
-      <c r="E80" s="42"/>
+      <c r="E80" s="86"/>
       <c r="F80" s="39">
         <f t="shared" ref="F80:F105" si="2">D80*E80</f>
         <v>0</v>
       </c>
-      <c r="G80" s="91" t="s">
+      <c r="G80" s="43" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1973,12 +1948,12 @@
       <c r="B81" s="23"/>
       <c r="C81" s="10"/>
       <c r="D81" s="23"/>
-      <c r="E81" s="43"/>
+      <c r="E81" s="86"/>
       <c r="F81" s="39">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="G81" s="91" t="s">
+      <c r="G81" s="43" t="s">
         <v>23</v>
       </c>
     </row>
@@ -1987,7 +1962,7 @@
       <c r="B82" s="23"/>
       <c r="C82" s="10"/>
       <c r="D82" s="30"/>
-      <c r="E82" s="43"/>
+      <c r="E82" s="86"/>
       <c r="F82" s="39">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -1998,7 +1973,7 @@
       <c r="B83" s="23"/>
       <c r="C83" s="10"/>
       <c r="D83" s="30"/>
-      <c r="E83" s="43"/>
+      <c r="E83" s="86"/>
       <c r="F83" s="39">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -2009,7 +1984,7 @@
       <c r="B84" s="23"/>
       <c r="C84" s="10"/>
       <c r="D84" s="30"/>
-      <c r="E84" s="43"/>
+      <c r="E84" s="86"/>
       <c r="F84" s="39">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -2020,7 +1995,7 @@
       <c r="B85" s="23"/>
       <c r="C85" s="10"/>
       <c r="D85" s="30"/>
-      <c r="E85" s="43"/>
+      <c r="E85" s="86"/>
       <c r="F85" s="39">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -2031,7 +2006,7 @@
       <c r="B86" s="23"/>
       <c r="C86" s="35"/>
       <c r="D86" s="30"/>
-      <c r="E86" s="43"/>
+      <c r="E86" s="86"/>
       <c r="F86" s="39">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -2042,7 +2017,7 @@
       <c r="B87" s="23"/>
       <c r="C87" s="10"/>
       <c r="D87" s="30"/>
-      <c r="E87" s="43"/>
+      <c r="E87" s="86"/>
       <c r="F87" s="39">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -2053,7 +2028,7 @@
       <c r="B88" s="23"/>
       <c r="C88" s="10"/>
       <c r="D88" s="30"/>
-      <c r="E88" s="43"/>
+      <c r="E88" s="86"/>
       <c r="F88" s="39">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -2064,7 +2039,7 @@
       <c r="B89" s="23"/>
       <c r="C89" s="10"/>
       <c r="D89" s="30"/>
-      <c r="E89" s="43"/>
+      <c r="E89" s="86"/>
       <c r="F89" s="39">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -2075,7 +2050,7 @@
       <c r="B90" s="23"/>
       <c r="C90" s="10"/>
       <c r="D90" s="30"/>
-      <c r="E90" s="40"/>
+      <c r="E90" s="86"/>
       <c r="F90" s="39">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -2086,7 +2061,7 @@
       <c r="B91" s="32"/>
       <c r="C91" s="31"/>
       <c r="D91" s="32"/>
-      <c r="E91" s="44"/>
+      <c r="E91" s="86"/>
       <c r="F91" s="39">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -2097,7 +2072,7 @@
       <c r="B92" s="32"/>
       <c r="C92" s="31"/>
       <c r="D92" s="32"/>
-      <c r="E92" s="44"/>
+      <c r="E92" s="86"/>
       <c r="F92" s="39">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -2108,7 +2083,7 @@
       <c r="B93" s="33"/>
       <c r="C93" s="36"/>
       <c r="D93" s="30"/>
-      <c r="E93" s="41"/>
+      <c r="E93" s="86"/>
       <c r="F93" s="39">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -2119,7 +2094,7 @@
       <c r="B94" s="25"/>
       <c r="C94" s="10"/>
       <c r="D94" s="30"/>
-      <c r="E94" s="40"/>
+      <c r="E94" s="86"/>
       <c r="F94" s="39">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -2130,7 +2105,7 @@
       <c r="B95" s="25"/>
       <c r="C95" s="10"/>
       <c r="D95" s="30"/>
-      <c r="E95" s="40"/>
+      <c r="E95" s="86"/>
       <c r="F95" s="39">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -2141,7 +2116,7 @@
       <c r="B96" s="25"/>
       <c r="C96" s="37"/>
       <c r="D96" s="30"/>
-      <c r="E96" s="40"/>
+      <c r="E96" s="86"/>
       <c r="F96" s="39">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -2152,7 +2127,7 @@
       <c r="B97" s="25"/>
       <c r="C97" s="10"/>
       <c r="D97" s="30"/>
-      <c r="E97" s="40"/>
+      <c r="E97" s="86"/>
       <c r="F97" s="39">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -2163,7 +2138,7 @@
       <c r="B98" s="24"/>
       <c r="C98" s="10"/>
       <c r="D98" s="30"/>
-      <c r="E98" s="40"/>
+      <c r="E98" s="86"/>
       <c r="F98" s="39">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -2174,7 +2149,7 @@
       <c r="B99" s="24"/>
       <c r="C99" s="10"/>
       <c r="D99" s="30"/>
-      <c r="E99" s="40"/>
+      <c r="E99" s="86"/>
       <c r="F99" s="39">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -2185,7 +2160,7 @@
       <c r="B100" s="24"/>
       <c r="C100" s="10"/>
       <c r="D100" s="30"/>
-      <c r="E100" s="40"/>
+      <c r="E100" s="86"/>
       <c r="F100" s="39">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -2196,7 +2171,7 @@
       <c r="B101" s="24"/>
       <c r="C101" s="10"/>
       <c r="D101" s="30"/>
-      <c r="E101" s="40"/>
+      <c r="E101" s="86"/>
       <c r="F101" s="39">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -2207,7 +2182,7 @@
       <c r="B102" s="24"/>
       <c r="C102" s="10"/>
       <c r="D102" s="30"/>
-      <c r="E102" s="40"/>
+      <c r="E102" s="86"/>
       <c r="F102" s="39">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -2218,7 +2193,7 @@
       <c r="B103" s="11"/>
       <c r="C103" s="37"/>
       <c r="D103" s="30"/>
-      <c r="E103" s="40"/>
+      <c r="E103" s="86"/>
       <c r="F103" s="39">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -2229,7 +2204,7 @@
       <c r="B104" s="11"/>
       <c r="C104" s="37"/>
       <c r="D104" s="30"/>
-      <c r="E104" s="40"/>
+      <c r="E104" s="86"/>
       <c r="F104" s="39">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -2240,7 +2215,7 @@
       <c r="B105" s="11"/>
       <c r="C105" s="37"/>
       <c r="D105" s="38"/>
-      <c r="E105" s="40"/>
+      <c r="E105" s="86"/>
       <c r="F105" s="39">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -2250,44 +2225,44 @@
       <c r="A106" s="12"/>
       <c r="B106" s="13"/>
       <c r="C106" s="14"/>
-      <c r="D106" s="78" t="s">
+      <c r="D106" s="73" t="s">
         <v>9</v>
       </c>
-      <c r="E106" s="79"/>
+      <c r="E106" s="74"/>
       <c r="F106" s="9">
         <f>SUM(F9:F105)</f>
         <v>0</v>
       </c>
     </row>
     <row r="107" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A107" s="88" t="s">
+      <c r="A107" s="83" t="s">
         <v>16</v>
       </c>
-      <c r="B107" s="89"/>
-      <c r="C107" s="89"/>
-      <c r="D107" s="89"/>
-      <c r="E107" s="89"/>
-      <c r="F107" s="90"/>
+      <c r="B107" s="84"/>
+      <c r="C107" s="84"/>
+      <c r="D107" s="84"/>
+      <c r="E107" s="84"/>
+      <c r="F107" s="85"/>
     </row>
     <row r="108" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A108" s="80"/>
-      <c r="B108" s="81"/>
-      <c r="C108" s="81"/>
-      <c r="D108" s="81"/>
-      <c r="E108" s="81"/>
-      <c r="F108" s="82"/>
+      <c r="A108" s="75"/>
+      <c r="B108" s="76"/>
+      <c r="C108" s="76"/>
+      <c r="D108" s="76"/>
+      <c r="E108" s="76"/>
+      <c r="F108" s="77"/>
     </row>
     <row r="109" spans="1:7" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A109" s="83" t="s">
+      <c r="A109" s="78" t="s">
         <v>10</v>
       </c>
-      <c r="B109" s="84"/>
-      <c r="C109" s="85"/>
-      <c r="D109" s="86" t="s">
+      <c r="B109" s="79"/>
+      <c r="C109" s="80"/>
+      <c r="D109" s="81" t="s">
         <v>11</v>
       </c>
-      <c r="E109" s="86"/>
-      <c r="F109" s="87"/>
+      <c r="E109" s="81"/>
+      <c r="F109" s="82"/>
     </row>
     <row r="110" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A110" s="3" t="s">
@@ -2295,9 +2270,9 @@
       </c>
       <c r="B110" s="15"/>
       <c r="C110" s="21"/>
-      <c r="D110" s="71"/>
-      <c r="E110" s="72"/>
-      <c r="F110" s="73"/>
+      <c r="D110" s="66"/>
+      <c r="E110" s="67"/>
+      <c r="F110" s="68"/>
     </row>
     <row r="111" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A111" s="3" t="s">
@@ -2305,9 +2280,9 @@
       </c>
       <c r="B111" s="15"/>
       <c r="C111" s="16"/>
-      <c r="D111" s="74"/>
-      <c r="E111" s="74"/>
-      <c r="F111" s="75"/>
+      <c r="D111" s="69"/>
+      <c r="E111" s="69"/>
+      <c r="F111" s="70"/>
     </row>
     <row r="112" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A112" s="17" t="s">
@@ -2315,12 +2290,12 @@
       </c>
       <c r="B112" s="18"/>
       <c r="C112" s="22"/>
-      <c r="D112" s="76" t="s">
+      <c r="D112" s="71" t="s">
         <v>15</v>
       </c>
-      <c r="E112" s="76"/>
-      <c r="F112" s="77"/>
-      <c r="G112" s="91" t="s">
+      <c r="E112" s="71"/>
+      <c r="F112" s="72"/>
+      <c r="G112" s="43" t="s">
         <v>21</v>
       </c>
     </row>
@@ -2331,7 +2306,7 @@
       <c r="D113" s="19"/>
       <c r="E113" s="19"/>
       <c r="F113" s="20"/>
-      <c r="G113" s="91" t="s">
+      <c r="G113" s="43" t="s">
         <v>24</v>
       </c>
     </row>

--- a/backend/templates/pr-template 3p.xlsx
+++ b/backend/templates/pr-template 3p.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\web-opr\backend\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27FF9B94-C5AA-4D52-A2C9-F3D5B7E03420}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1090453-91B5-4D7B-8278-4946442D801C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -418,9 +418,6 @@
     <xf numFmtId="164" fontId="9" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -477,22 +474,12 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -508,11 +495,26 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -636,8 +638,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1082,8 +1084,8 @@
       <c r="A4" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="26"/>
-      <c r="C4" s="27"/>
+      <c r="B4" s="25"/>
+      <c r="C4" s="26"/>
       <c r="D4" s="60"/>
       <c r="E4" s="60"/>
       <c r="F4" s="61"/>
@@ -1143,1088 +1145,1088 @@
       <c r="F8" s="51"/>
     </row>
     <row r="9" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="41"/>
-      <c r="B9" s="42"/>
-      <c r="C9" s="40"/>
-      <c r="D9" s="40"/>
-      <c r="E9" s="86"/>
-      <c r="F9" s="39">
+      <c r="A9" s="36"/>
+      <c r="B9" s="27"/>
+      <c r="C9" s="86"/>
+      <c r="D9" s="35"/>
+      <c r="E9" s="38"/>
+      <c r="F9" s="34">
         <f t="shared" ref="F9:F45" si="0">D9*E9</f>
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="41"/>
-      <c r="B10" s="42"/>
-      <c r="C10" s="40"/>
-      <c r="D10" s="40"/>
-      <c r="E10" s="86"/>
-      <c r="F10" s="39">
+      <c r="A10" s="36"/>
+      <c r="B10" s="27"/>
+      <c r="C10" s="86"/>
+      <c r="D10" s="35"/>
+      <c r="E10" s="38"/>
+      <c r="F10" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="41"/>
-      <c r="B11" s="42"/>
-      <c r="C11" s="40"/>
-      <c r="D11" s="40"/>
-      <c r="E11" s="86"/>
-      <c r="F11" s="39">
+      <c r="A11" s="36"/>
+      <c r="B11" s="27"/>
+      <c r="C11" s="86"/>
+      <c r="D11" s="35"/>
+      <c r="E11" s="38"/>
+      <c r="F11" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="41"/>
-      <c r="B12" s="42"/>
-      <c r="C12" s="40"/>
-      <c r="D12" s="40"/>
-      <c r="E12" s="86"/>
-      <c r="F12" s="39">
+      <c r="A12" s="36"/>
+      <c r="B12" s="27"/>
+      <c r="C12" s="86"/>
+      <c r="D12" s="35"/>
+      <c r="E12" s="38"/>
+      <c r="F12" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="41"/>
-      <c r="B13" s="42"/>
-      <c r="C13" s="40"/>
-      <c r="D13" s="40"/>
-      <c r="E13" s="86"/>
-      <c r="F13" s="39">
+      <c r="A13" s="36"/>
+      <c r="B13" s="27"/>
+      <c r="C13" s="86"/>
+      <c r="D13" s="35"/>
+      <c r="E13" s="38"/>
+      <c r="F13" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="41"/>
-      <c r="B14" s="42"/>
-      <c r="C14" s="40"/>
-      <c r="D14" s="40"/>
-      <c r="E14" s="86"/>
-      <c r="F14" s="39">
+      <c r="A14" s="36"/>
+      <c r="B14" s="27"/>
+      <c r="C14" s="86"/>
+      <c r="D14" s="35"/>
+      <c r="E14" s="38"/>
+      <c r="F14" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="41"/>
-      <c r="B15" s="42"/>
-      <c r="C15" s="40"/>
-      <c r="D15" s="40"/>
-      <c r="E15" s="86"/>
-      <c r="F15" s="39">
+      <c r="A15" s="36"/>
+      <c r="B15" s="27"/>
+      <c r="C15" s="86"/>
+      <c r="D15" s="35"/>
+      <c r="E15" s="38"/>
+      <c r="F15" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="41"/>
-      <c r="B16" s="42"/>
-      <c r="C16" s="40"/>
-      <c r="D16" s="40"/>
-      <c r="E16" s="86"/>
-      <c r="F16" s="39">
+      <c r="A16" s="36"/>
+      <c r="B16" s="27"/>
+      <c r="C16" s="86"/>
+      <c r="D16" s="35"/>
+      <c r="E16" s="38"/>
+      <c r="F16" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="41"/>
-      <c r="B17" s="42"/>
-      <c r="C17" s="40"/>
-      <c r="D17" s="40"/>
-      <c r="E17" s="86"/>
-      <c r="F17" s="39">
+      <c r="A17" s="36"/>
+      <c r="B17" s="27"/>
+      <c r="C17" s="86"/>
+      <c r="D17" s="35"/>
+      <c r="E17" s="38"/>
+      <c r="F17" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="41"/>
-      <c r="B18" s="42"/>
-      <c r="C18" s="40"/>
-      <c r="D18" s="40"/>
-      <c r="E18" s="86"/>
-      <c r="F18" s="39">
+      <c r="A18" s="36"/>
+      <c r="B18" s="27"/>
+      <c r="C18" s="86"/>
+      <c r="D18" s="35"/>
+      <c r="E18" s="38"/>
+      <c r="F18" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="41"/>
-      <c r="B19" s="42"/>
-      <c r="C19" s="40"/>
-      <c r="D19" s="40"/>
-      <c r="E19" s="86"/>
-      <c r="F19" s="39">
+      <c r="A19" s="36"/>
+      <c r="B19" s="27"/>
+      <c r="C19" s="86"/>
+      <c r="D19" s="35"/>
+      <c r="E19" s="38"/>
+      <c r="F19" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="41"/>
-      <c r="B20" s="42"/>
-      <c r="C20" s="40"/>
-      <c r="D20" s="40"/>
-      <c r="E20" s="86"/>
-      <c r="F20" s="39">
+      <c r="A20" s="36"/>
+      <c r="B20" s="27"/>
+      <c r="C20" s="86"/>
+      <c r="D20" s="35"/>
+      <c r="E20" s="38"/>
+      <c r="F20" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="41"/>
-      <c r="B21" s="42"/>
-      <c r="C21" s="40"/>
-      <c r="D21" s="40"/>
-      <c r="E21" s="86"/>
-      <c r="F21" s="39">
+      <c r="A21" s="36"/>
+      <c r="B21" s="27"/>
+      <c r="C21" s="86"/>
+      <c r="D21" s="35"/>
+      <c r="E21" s="38"/>
+      <c r="F21" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="41"/>
-      <c r="B22" s="42"/>
-      <c r="C22" s="40"/>
-      <c r="D22" s="40"/>
-      <c r="E22" s="86"/>
-      <c r="F22" s="39">
+      <c r="A22" s="36"/>
+      <c r="B22" s="27"/>
+      <c r="C22" s="86"/>
+      <c r="D22" s="35"/>
+      <c r="E22" s="38"/>
+      <c r="F22" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="41"/>
-      <c r="B23" s="42"/>
-      <c r="C23" s="40"/>
-      <c r="D23" s="40"/>
-      <c r="E23" s="86"/>
-      <c r="F23" s="39">
+      <c r="A23" s="36"/>
+      <c r="B23" s="27"/>
+      <c r="C23" s="86"/>
+      <c r="D23" s="35"/>
+      <c r="E23" s="38"/>
+      <c r="F23" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="41"/>
-      <c r="B24" s="42"/>
-      <c r="C24" s="40"/>
-      <c r="D24" s="40"/>
-      <c r="E24" s="86"/>
-      <c r="F24" s="39">
+      <c r="A24" s="36"/>
+      <c r="B24" s="27"/>
+      <c r="C24" s="86"/>
+      <c r="D24" s="35"/>
+      <c r="E24" s="38"/>
+      <c r="F24" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="41"/>
-      <c r="B25" s="42"/>
-      <c r="C25" s="40"/>
-      <c r="D25" s="40"/>
-      <c r="E25" s="86"/>
-      <c r="F25" s="39">
+      <c r="A25" s="36"/>
+      <c r="B25" s="27"/>
+      <c r="C25" s="86"/>
+      <c r="D25" s="35"/>
+      <c r="E25" s="38"/>
+      <c r="F25" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="41"/>
-      <c r="B26" s="42"/>
-      <c r="C26" s="40"/>
-      <c r="D26" s="40"/>
-      <c r="E26" s="86"/>
-      <c r="F26" s="39">
+      <c r="A26" s="36"/>
+      <c r="B26" s="27"/>
+      <c r="C26" s="86"/>
+      <c r="D26" s="35"/>
+      <c r="E26" s="38"/>
+      <c r="F26" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="41"/>
-      <c r="B27" s="42"/>
-      <c r="C27" s="40"/>
-      <c r="D27" s="40"/>
-      <c r="E27" s="86"/>
-      <c r="F27" s="39">
+      <c r="A27" s="36"/>
+      <c r="B27" s="27"/>
+      <c r="C27" s="86"/>
+      <c r="D27" s="35"/>
+      <c r="E27" s="38"/>
+      <c r="F27" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="41"/>
-      <c r="B28" s="42"/>
-      <c r="C28" s="40"/>
-      <c r="D28" s="40"/>
-      <c r="E28" s="86"/>
-      <c r="F28" s="39">
+      <c r="A28" s="36"/>
+      <c r="B28" s="27"/>
+      <c r="C28" s="86"/>
+      <c r="D28" s="35"/>
+      <c r="E28" s="38"/>
+      <c r="F28" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="41"/>
-      <c r="B29" s="42"/>
-      <c r="C29" s="40"/>
-      <c r="D29" s="40"/>
-      <c r="E29" s="86"/>
-      <c r="F29" s="39">
+      <c r="A29" s="36"/>
+      <c r="B29" s="27"/>
+      <c r="C29" s="86"/>
+      <c r="D29" s="35"/>
+      <c r="E29" s="38"/>
+      <c r="F29" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="41"/>
-      <c r="B30" s="42"/>
-      <c r="C30" s="40"/>
-      <c r="D30" s="40"/>
-      <c r="E30" s="86"/>
-      <c r="F30" s="39">
+      <c r="A30" s="36"/>
+      <c r="B30" s="27"/>
+      <c r="C30" s="86"/>
+      <c r="D30" s="35"/>
+      <c r="E30" s="38"/>
+      <c r="F30" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="41"/>
-      <c r="B31" s="42"/>
-      <c r="C31" s="40"/>
-      <c r="D31" s="40"/>
-      <c r="E31" s="86"/>
-      <c r="F31" s="39">
+      <c r="A31" s="36"/>
+      <c r="B31" s="27"/>
+      <c r="C31" s="86"/>
+      <c r="D31" s="35"/>
+      <c r="E31" s="38"/>
+      <c r="F31" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="41"/>
-      <c r="B32" s="42"/>
-      <c r="C32" s="40"/>
-      <c r="D32" s="40"/>
-      <c r="E32" s="86"/>
-      <c r="F32" s="39">
+      <c r="A32" s="36"/>
+      <c r="B32" s="27"/>
+      <c r="C32" s="86"/>
+      <c r="D32" s="35"/>
+      <c r="E32" s="38"/>
+      <c r="F32" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="41"/>
-      <c r="B33" s="42"/>
-      <c r="C33" s="40"/>
-      <c r="D33" s="40"/>
-      <c r="E33" s="86"/>
-      <c r="F33" s="39">
+      <c r="A33" s="36"/>
+      <c r="B33" s="27"/>
+      <c r="C33" s="86"/>
+      <c r="D33" s="35"/>
+      <c r="E33" s="38"/>
+      <c r="F33" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="41"/>
-      <c r="B34" s="42"/>
-      <c r="C34" s="40"/>
-      <c r="D34" s="40"/>
-      <c r="E34" s="86"/>
-      <c r="F34" s="39">
+      <c r="A34" s="36"/>
+      <c r="B34" s="27"/>
+      <c r="C34" s="86"/>
+      <c r="D34" s="35"/>
+      <c r="E34" s="38"/>
+      <c r="F34" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="41"/>
-      <c r="B35" s="42"/>
-      <c r="C35" s="40"/>
-      <c r="D35" s="40"/>
-      <c r="E35" s="86"/>
-      <c r="F35" s="39">
+      <c r="A35" s="36"/>
+      <c r="B35" s="27"/>
+      <c r="C35" s="86"/>
+      <c r="D35" s="35"/>
+      <c r="E35" s="38"/>
+      <c r="F35" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="41"/>
-      <c r="B36" s="42"/>
-      <c r="C36" s="40"/>
-      <c r="D36" s="40"/>
-      <c r="E36" s="86"/>
-      <c r="F36" s="39">
+      <c r="A36" s="36"/>
+      <c r="B36" s="27"/>
+      <c r="C36" s="86"/>
+      <c r="D36" s="35"/>
+      <c r="E36" s="38"/>
+      <c r="F36" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="41"/>
-      <c r="B37" s="42"/>
-      <c r="C37" s="40"/>
-      <c r="D37" s="40"/>
-      <c r="E37" s="86"/>
-      <c r="F37" s="39">
+      <c r="A37" s="36"/>
+      <c r="B37" s="27"/>
+      <c r="C37" s="86"/>
+      <c r="D37" s="35"/>
+      <c r="E37" s="38"/>
+      <c r="F37" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="41"/>
-      <c r="B38" s="42"/>
-      <c r="C38" s="40"/>
-      <c r="D38" s="40"/>
-      <c r="E38" s="86"/>
-      <c r="F38" s="39">
+      <c r="A38" s="36"/>
+      <c r="B38" s="27"/>
+      <c r="C38" s="86"/>
+      <c r="D38" s="35"/>
+      <c r="E38" s="38"/>
+      <c r="F38" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="41"/>
-      <c r="B39" s="42"/>
-      <c r="C39" s="40"/>
-      <c r="D39" s="40"/>
-      <c r="E39" s="86"/>
-      <c r="F39" s="39">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G39" s="43" t="s">
+      <c r="A39" s="36"/>
+      <c r="B39" s="27"/>
+      <c r="C39" s="86"/>
+      <c r="D39" s="35"/>
+      <c r="E39" s="38"/>
+      <c r="F39" s="34">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G39" s="37" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="41"/>
-      <c r="B40" s="42"/>
-      <c r="C40" s="40"/>
-      <c r="D40" s="40"/>
-      <c r="E40" s="86"/>
-      <c r="F40" s="39">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G40" s="43" t="s">
+      <c r="A40" s="36"/>
+      <c r="B40" s="27"/>
+      <c r="C40" s="86"/>
+      <c r="D40" s="35"/>
+      <c r="E40" s="38"/>
+      <c r="F40" s="34">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G40" s="37" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="41"/>
-      <c r="B41" s="42"/>
-      <c r="C41" s="40"/>
-      <c r="D41" s="40"/>
-      <c r="E41" s="86"/>
-      <c r="F41" s="39">
+      <c r="A41" s="36"/>
+      <c r="B41" s="27"/>
+      <c r="C41" s="86"/>
+      <c r="D41" s="35"/>
+      <c r="E41" s="38"/>
+      <c r="F41" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="41"/>
-      <c r="B42" s="42"/>
-      <c r="C42" s="40"/>
-      <c r="D42" s="40"/>
-      <c r="E42" s="86"/>
-      <c r="F42" s="39">
+      <c r="A42" s="36"/>
+      <c r="B42" s="27"/>
+      <c r="C42" s="86"/>
+      <c r="D42" s="35"/>
+      <c r="E42" s="38"/>
+      <c r="F42" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="41"/>
-      <c r="B43" s="42"/>
-      <c r="C43" s="40"/>
-      <c r="D43" s="40"/>
-      <c r="E43" s="86"/>
-      <c r="F43" s="39">
+      <c r="A43" s="36"/>
+      <c r="B43" s="27"/>
+      <c r="C43" s="86"/>
+      <c r="D43" s="35"/>
+      <c r="E43" s="38"/>
+      <c r="F43" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="41"/>
-      <c r="B44" s="42"/>
-      <c r="C44" s="40"/>
-      <c r="D44" s="40"/>
-      <c r="E44" s="86"/>
-      <c r="F44" s="39">
+      <c r="A44" s="36"/>
+      <c r="B44" s="27"/>
+      <c r="C44" s="86"/>
+      <c r="D44" s="35"/>
+      <c r="E44" s="38"/>
+      <c r="F44" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="41"/>
-      <c r="B45" s="42"/>
-      <c r="C45" s="40"/>
-      <c r="D45" s="40"/>
-      <c r="E45" s="86"/>
-      <c r="F45" s="39">
+      <c r="A45" s="36"/>
+      <c r="B45" s="27"/>
+      <c r="C45" s="86"/>
+      <c r="D45" s="35"/>
+      <c r="E45" s="38"/>
+      <c r="F45" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="41"/>
-      <c r="B46" s="42"/>
-      <c r="C46" s="40"/>
-      <c r="D46" s="40"/>
-      <c r="E46" s="86"/>
-      <c r="F46" s="39">
+      <c r="A46" s="36"/>
+      <c r="B46" s="27"/>
+      <c r="C46" s="86"/>
+      <c r="D46" s="35"/>
+      <c r="E46" s="38"/>
+      <c r="F46" s="34">
         <f t="shared" ref="F46:F79" si="1">D46*E46</f>
         <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="41"/>
-      <c r="B47" s="42"/>
-      <c r="C47" s="40"/>
-      <c r="D47" s="40"/>
-      <c r="E47" s="86"/>
-      <c r="F47" s="39">
+      <c r="A47" s="36"/>
+      <c r="B47" s="27"/>
+      <c r="C47" s="86"/>
+      <c r="D47" s="35"/>
+      <c r="E47" s="38"/>
+      <c r="F47" s="34">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="41"/>
-      <c r="B48" s="42"/>
-      <c r="C48" s="40"/>
-      <c r="D48" s="40"/>
-      <c r="E48" s="86"/>
-      <c r="F48" s="39">
+      <c r="A48" s="36"/>
+      <c r="B48" s="27"/>
+      <c r="C48" s="86"/>
+      <c r="D48" s="35"/>
+      <c r="E48" s="38"/>
+      <c r="F48" s="34">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="41"/>
-      <c r="B49" s="42"/>
-      <c r="C49" s="40"/>
-      <c r="D49" s="40"/>
-      <c r="E49" s="86"/>
-      <c r="F49" s="39">
+      <c r="A49" s="36"/>
+      <c r="B49" s="27"/>
+      <c r="C49" s="86"/>
+      <c r="D49" s="35"/>
+      <c r="E49" s="38"/>
+      <c r="F49" s="34">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="41"/>
-      <c r="B50" s="42"/>
-      <c r="C50" s="40"/>
-      <c r="D50" s="40"/>
-      <c r="E50" s="86"/>
-      <c r="F50" s="39">
+      <c r="A50" s="36"/>
+      <c r="B50" s="27"/>
+      <c r="C50" s="86"/>
+      <c r="D50" s="35"/>
+      <c r="E50" s="38"/>
+      <c r="F50" s="34">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="41"/>
-      <c r="B51" s="42"/>
-      <c r="C51" s="40"/>
-      <c r="D51" s="40"/>
-      <c r="E51" s="86"/>
-      <c r="F51" s="39">
+      <c r="A51" s="36"/>
+      <c r="B51" s="27"/>
+      <c r="C51" s="86"/>
+      <c r="D51" s="35"/>
+      <c r="E51" s="38"/>
+      <c r="F51" s="34">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="41"/>
-      <c r="B52" s="42"/>
-      <c r="C52" s="40"/>
-      <c r="D52" s="40"/>
-      <c r="E52" s="86"/>
-      <c r="F52" s="39">
+      <c r="A52" s="36"/>
+      <c r="B52" s="27"/>
+      <c r="C52" s="86"/>
+      <c r="D52" s="35"/>
+      <c r="E52" s="38"/>
+      <c r="F52" s="34">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="41"/>
-      <c r="B53" s="42"/>
-      <c r="C53" s="40"/>
-      <c r="D53" s="40"/>
-      <c r="E53" s="86"/>
-      <c r="F53" s="39">
+      <c r="A53" s="36"/>
+      <c r="B53" s="27"/>
+      <c r="C53" s="86"/>
+      <c r="D53" s="35"/>
+      <c r="E53" s="38"/>
+      <c r="F53" s="34">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="41"/>
-      <c r="B54" s="42"/>
-      <c r="C54" s="40"/>
-      <c r="D54" s="40"/>
-      <c r="E54" s="86"/>
-      <c r="F54" s="39">
+      <c r="A54" s="36"/>
+      <c r="B54" s="27"/>
+      <c r="C54" s="86"/>
+      <c r="D54" s="35"/>
+      <c r="E54" s="38"/>
+      <c r="F54" s="34">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="41"/>
-      <c r="B55" s="42"/>
-      <c r="C55" s="40"/>
-      <c r="D55" s="40"/>
-      <c r="E55" s="86"/>
-      <c r="F55" s="39">
+      <c r="A55" s="36"/>
+      <c r="B55" s="27"/>
+      <c r="C55" s="86"/>
+      <c r="D55" s="35"/>
+      <c r="E55" s="38"/>
+      <c r="F55" s="34">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="41"/>
-      <c r="B56" s="42"/>
-      <c r="C56" s="40"/>
-      <c r="D56" s="40"/>
-      <c r="E56" s="86"/>
-      <c r="F56" s="39">
+      <c r="A56" s="36"/>
+      <c r="B56" s="27"/>
+      <c r="C56" s="86"/>
+      <c r="D56" s="35"/>
+      <c r="E56" s="38"/>
+      <c r="F56" s="34">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="41"/>
-      <c r="B57" s="42"/>
-      <c r="C57" s="40"/>
-      <c r="D57" s="40"/>
-      <c r="E57" s="86"/>
-      <c r="F57" s="39">
+      <c r="A57" s="36"/>
+      <c r="B57" s="27"/>
+      <c r="C57" s="86"/>
+      <c r="D57" s="35"/>
+      <c r="E57" s="38"/>
+      <c r="F57" s="34">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A58" s="41"/>
-      <c r="B58" s="42"/>
-      <c r="C58" s="40"/>
-      <c r="D58" s="40"/>
-      <c r="E58" s="86"/>
-      <c r="F58" s="39">
+      <c r="A58" s="36"/>
+      <c r="B58" s="27"/>
+      <c r="C58" s="86"/>
+      <c r="D58" s="35"/>
+      <c r="E58" s="38"/>
+      <c r="F58" s="34">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A59" s="41"/>
-      <c r="B59" s="42"/>
-      <c r="C59" s="40"/>
-      <c r="D59" s="40"/>
-      <c r="E59" s="86"/>
-      <c r="F59" s="39">
+      <c r="A59" s="36"/>
+      <c r="B59" s="27"/>
+      <c r="C59" s="86"/>
+      <c r="D59" s="35"/>
+      <c r="E59" s="38"/>
+      <c r="F59" s="34">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="41"/>
-      <c r="B60" s="42"/>
-      <c r="C60" s="40"/>
-      <c r="D60" s="40"/>
-      <c r="E60" s="86"/>
-      <c r="F60" s="39">
+      <c r="A60" s="36"/>
+      <c r="B60" s="27"/>
+      <c r="C60" s="86"/>
+      <c r="D60" s="35"/>
+      <c r="E60" s="38"/>
+      <c r="F60" s="34">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="41"/>
-      <c r="B61" s="42"/>
-      <c r="C61" s="40"/>
-      <c r="D61" s="40"/>
-      <c r="E61" s="86"/>
-      <c r="F61" s="39">
+      <c r="A61" s="36"/>
+      <c r="B61" s="27"/>
+      <c r="C61" s="86"/>
+      <c r="D61" s="35"/>
+      <c r="E61" s="38"/>
+      <c r="F61" s="34">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="41"/>
-      <c r="B62" s="42"/>
-      <c r="C62" s="40"/>
-      <c r="D62" s="40"/>
-      <c r="E62" s="86"/>
-      <c r="F62" s="39">
+      <c r="A62" s="36"/>
+      <c r="B62" s="27"/>
+      <c r="C62" s="86"/>
+      <c r="D62" s="35"/>
+      <c r="E62" s="38"/>
+      <c r="F62" s="34">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="41"/>
-      <c r="B63" s="42"/>
-      <c r="C63" s="40"/>
-      <c r="D63" s="40"/>
-      <c r="E63" s="86"/>
-      <c r="F63" s="39">
+      <c r="A63" s="36"/>
+      <c r="B63" s="27"/>
+      <c r="C63" s="86"/>
+      <c r="D63" s="35"/>
+      <c r="E63" s="38"/>
+      <c r="F63" s="34">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="41"/>
-      <c r="B64" s="42"/>
-      <c r="C64" s="40"/>
-      <c r="D64" s="40"/>
-      <c r="E64" s="86"/>
-      <c r="F64" s="39">
+      <c r="A64" s="36"/>
+      <c r="B64" s="27"/>
+      <c r="C64" s="86"/>
+      <c r="D64" s="35"/>
+      <c r="E64" s="38"/>
+      <c r="F64" s="34">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="41"/>
-      <c r="B65" s="42"/>
-      <c r="C65" s="40"/>
-      <c r="D65" s="40"/>
-      <c r="E65" s="86"/>
-      <c r="F65" s="39">
+      <c r="A65" s="36"/>
+      <c r="B65" s="27"/>
+      <c r="C65" s="86"/>
+      <c r="D65" s="35"/>
+      <c r="E65" s="38"/>
+      <c r="F65" s="34">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A66" s="41"/>
-      <c r="B66" s="42"/>
-      <c r="C66" s="40"/>
-      <c r="D66" s="40"/>
-      <c r="E66" s="86"/>
-      <c r="F66" s="39">
+      <c r="A66" s="36"/>
+      <c r="B66" s="27"/>
+      <c r="C66" s="86"/>
+      <c r="D66" s="35"/>
+      <c r="E66" s="38"/>
+      <c r="F66" s="34">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="67" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A67" s="41"/>
-      <c r="B67" s="42"/>
-      <c r="C67" s="40"/>
-      <c r="D67" s="40"/>
-      <c r="E67" s="86"/>
-      <c r="F67" s="39">
+      <c r="A67" s="36"/>
+      <c r="B67" s="27"/>
+      <c r="C67" s="86"/>
+      <c r="D67" s="35"/>
+      <c r="E67" s="38"/>
+      <c r="F67" s="34">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="68" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="41"/>
-      <c r="B68" s="42"/>
-      <c r="C68" s="40"/>
-      <c r="D68" s="40"/>
-      <c r="E68" s="86"/>
-      <c r="F68" s="39">
+      <c r="A68" s="36"/>
+      <c r="B68" s="27"/>
+      <c r="C68" s="86"/>
+      <c r="D68" s="35"/>
+      <c r="E68" s="38"/>
+      <c r="F68" s="34">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="41"/>
-      <c r="B69" s="42"/>
-      <c r="C69" s="40"/>
-      <c r="D69" s="40"/>
-      <c r="E69" s="86"/>
-      <c r="F69" s="39">
+      <c r="A69" s="36"/>
+      <c r="B69" s="27"/>
+      <c r="C69" s="86"/>
+      <c r="D69" s="35"/>
+      <c r="E69" s="38"/>
+      <c r="F69" s="34">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="41"/>
-      <c r="B70" s="42"/>
-      <c r="C70" s="40"/>
-      <c r="D70" s="40"/>
-      <c r="E70" s="86"/>
-      <c r="F70" s="39">
+      <c r="A70" s="36"/>
+      <c r="B70" s="27"/>
+      <c r="C70" s="86"/>
+      <c r="D70" s="35"/>
+      <c r="E70" s="38"/>
+      <c r="F70" s="34">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="41"/>
-      <c r="B71" s="42"/>
-      <c r="C71" s="40"/>
-      <c r="D71" s="40"/>
-      <c r="E71" s="86"/>
-      <c r="F71" s="39">
+      <c r="A71" s="36"/>
+      <c r="B71" s="27"/>
+      <c r="C71" s="86"/>
+      <c r="D71" s="35"/>
+      <c r="E71" s="38"/>
+      <c r="F71" s="34">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="41"/>
-      <c r="B72" s="42"/>
-      <c r="C72" s="40"/>
-      <c r="D72" s="40"/>
-      <c r="E72" s="86"/>
-      <c r="F72" s="39">
+      <c r="A72" s="36"/>
+      <c r="B72" s="27"/>
+      <c r="C72" s="86"/>
+      <c r="D72" s="35"/>
+      <c r="E72" s="38"/>
+      <c r="F72" s="34">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="41"/>
-      <c r="B73" s="42"/>
-      <c r="C73" s="40"/>
-      <c r="D73" s="40"/>
-      <c r="E73" s="86"/>
-      <c r="F73" s="39">
+      <c r="A73" s="36"/>
+      <c r="B73" s="27"/>
+      <c r="C73" s="86"/>
+      <c r="D73" s="35"/>
+      <c r="E73" s="38"/>
+      <c r="F73" s="34">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A74" s="41"/>
-      <c r="B74" s="42"/>
-      <c r="C74" s="40"/>
-      <c r="D74" s="40"/>
-      <c r="E74" s="86"/>
-      <c r="F74" s="39">
+      <c r="A74" s="36"/>
+      <c r="B74" s="27"/>
+      <c r="C74" s="86"/>
+      <c r="D74" s="35"/>
+      <c r="E74" s="38"/>
+      <c r="F74" s="34">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A75" s="41"/>
-      <c r="B75" s="42"/>
-      <c r="C75" s="40"/>
-      <c r="D75" s="40"/>
-      <c r="E75" s="86"/>
-      <c r="F75" s="39">
+      <c r="A75" s="36"/>
+      <c r="B75" s="27"/>
+      <c r="C75" s="86"/>
+      <c r="D75" s="35"/>
+      <c r="E75" s="38"/>
+      <c r="F75" s="34">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="41"/>
-      <c r="B76" s="42"/>
-      <c r="C76" s="40"/>
-      <c r="D76" s="40"/>
-      <c r="E76" s="86"/>
-      <c r="F76" s="39">
+      <c r="A76" s="36"/>
+      <c r="B76" s="27"/>
+      <c r="C76" s="86"/>
+      <c r="D76" s="35"/>
+      <c r="E76" s="38"/>
+      <c r="F76" s="34">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="77" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="41"/>
-      <c r="B77" s="42"/>
-      <c r="C77" s="40"/>
-      <c r="D77" s="40"/>
-      <c r="E77" s="86"/>
-      <c r="F77" s="39">
+      <c r="A77" s="36"/>
+      <c r="B77" s="27"/>
+      <c r="C77" s="86"/>
+      <c r="D77" s="35"/>
+      <c r="E77" s="38"/>
+      <c r="F77" s="34">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="41"/>
-      <c r="B78" s="42"/>
-      <c r="C78" s="40"/>
-      <c r="D78" s="40"/>
-      <c r="E78" s="86"/>
-      <c r="F78" s="39">
+      <c r="A78" s="36"/>
+      <c r="B78" s="27"/>
+      <c r="C78" s="86"/>
+      <c r="D78" s="35"/>
+      <c r="E78" s="38"/>
+      <c r="F78" s="34">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="79" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="41"/>
-      <c r="B79" s="42"/>
-      <c r="C79" s="40"/>
-      <c r="D79" s="40"/>
-      <c r="E79" s="86"/>
-      <c r="F79" s="39">
+      <c r="A79" s="36"/>
+      <c r="B79" s="27"/>
+      <c r="C79" s="86"/>
+      <c r="D79" s="35"/>
+      <c r="E79" s="38"/>
+      <c r="F79" s="34">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:7" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="8"/>
-      <c r="B80" s="28"/>
-      <c r="C80" s="34"/>
-      <c r="D80" s="29"/>
-      <c r="E80" s="86"/>
-      <c r="F80" s="39">
+      <c r="B80" s="27"/>
+      <c r="C80" s="39"/>
+      <c r="D80" s="28"/>
+      <c r="E80" s="38"/>
+      <c r="F80" s="34">
         <f t="shared" ref="F80:F105" si="2">D80*E80</f>
         <v>0</v>
       </c>
-      <c r="G80" s="43" t="s">
+      <c r="G80" s="37" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="81" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="8"/>
-      <c r="B81" s="23"/>
-      <c r="C81" s="10"/>
-      <c r="D81" s="23"/>
-      <c r="E81" s="86"/>
-      <c r="F81" s="39">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G81" s="43" t="s">
+      <c r="B81" s="22"/>
+      <c r="C81" s="40"/>
+      <c r="D81" s="22"/>
+      <c r="E81" s="38"/>
+      <c r="F81" s="34">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G81" s="37" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="82" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A82" s="8"/>
-      <c r="B82" s="23"/>
-      <c r="C82" s="10"/>
-      <c r="D82" s="30"/>
-      <c r="E82" s="86"/>
-      <c r="F82" s="39">
+      <c r="B82" s="22"/>
+      <c r="C82" s="40"/>
+      <c r="D82" s="29"/>
+      <c r="E82" s="38"/>
+      <c r="F82" s="34">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="83" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" s="8"/>
-      <c r="B83" s="23"/>
-      <c r="C83" s="10"/>
-      <c r="D83" s="30"/>
-      <c r="E83" s="86"/>
-      <c r="F83" s="39">
+      <c r="B83" s="22"/>
+      <c r="C83" s="40"/>
+      <c r="D83" s="29"/>
+      <c r="E83" s="38"/>
+      <c r="F83" s="34">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="84" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" s="8"/>
-      <c r="B84" s="23"/>
-      <c r="C84" s="10"/>
-      <c r="D84" s="30"/>
-      <c r="E84" s="86"/>
-      <c r="F84" s="39">
+      <c r="B84" s="22"/>
+      <c r="C84" s="40"/>
+      <c r="D84" s="29"/>
+      <c r="E84" s="38"/>
+      <c r="F84" s="34">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="85" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" s="8"/>
-      <c r="B85" s="23"/>
-      <c r="C85" s="10"/>
-      <c r="D85" s="30"/>
-      <c r="E85" s="86"/>
-      <c r="F85" s="39">
+      <c r="B85" s="22"/>
+      <c r="C85" s="40"/>
+      <c r="D85" s="29"/>
+      <c r="E85" s="38"/>
+      <c r="F85" s="34">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="86" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" s="8"/>
-      <c r="B86" s="23"/>
-      <c r="C86" s="35"/>
-      <c r="D86" s="30"/>
-      <c r="E86" s="86"/>
-      <c r="F86" s="39">
+      <c r="B86" s="22"/>
+      <c r="C86" s="41"/>
+      <c r="D86" s="29"/>
+      <c r="E86" s="38"/>
+      <c r="F86" s="34">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="87" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="8"/>
-      <c r="B87" s="23"/>
-      <c r="C87" s="10"/>
-      <c r="D87" s="30"/>
-      <c r="E87" s="86"/>
-      <c r="F87" s="39">
+      <c r="B87" s="22"/>
+      <c r="C87" s="40"/>
+      <c r="D87" s="29"/>
+      <c r="E87" s="38"/>
+      <c r="F87" s="34">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="88" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="8"/>
-      <c r="B88" s="23"/>
-      <c r="C88" s="10"/>
-      <c r="D88" s="30"/>
-      <c r="E88" s="86"/>
-      <c r="F88" s="39">
+      <c r="B88" s="22"/>
+      <c r="C88" s="40"/>
+      <c r="D88" s="29"/>
+      <c r="E88" s="38"/>
+      <c r="F88" s="34">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="89" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89" s="8"/>
-      <c r="B89" s="23"/>
-      <c r="C89" s="10"/>
-      <c r="D89" s="30"/>
-      <c r="E89" s="86"/>
-      <c r="F89" s="39">
+      <c r="B89" s="22"/>
+      <c r="C89" s="40"/>
+      <c r="D89" s="29"/>
+      <c r="E89" s="38"/>
+      <c r="F89" s="34">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="90" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A90" s="8"/>
-      <c r="B90" s="23"/>
-      <c r="C90" s="10"/>
-      <c r="D90" s="30"/>
-      <c r="E90" s="86"/>
-      <c r="F90" s="39">
+      <c r="B90" s="22"/>
+      <c r="C90" s="40"/>
+      <c r="D90" s="29"/>
+      <c r="E90" s="38"/>
+      <c r="F90" s="34">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="91" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A91" s="8"/>
-      <c r="B91" s="32"/>
-      <c r="C91" s="31"/>
-      <c r="D91" s="32"/>
-      <c r="E91" s="86"/>
-      <c r="F91" s="39">
+      <c r="B91" s="30"/>
+      <c r="C91" s="42"/>
+      <c r="D91" s="30"/>
+      <c r="E91" s="38"/>
+      <c r="F91" s="34">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="92" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" s="8"/>
-      <c r="B92" s="32"/>
-      <c r="C92" s="31"/>
-      <c r="D92" s="32"/>
-      <c r="E92" s="86"/>
-      <c r="F92" s="39">
+      <c r="B92" s="30"/>
+      <c r="C92" s="42"/>
+      <c r="D92" s="30"/>
+      <c r="E92" s="38"/>
+      <c r="F92" s="34">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="93" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="8"/>
-      <c r="B93" s="33"/>
-      <c r="C93" s="36"/>
-      <c r="D93" s="30"/>
-      <c r="E93" s="86"/>
-      <c r="F93" s="39">
+      <c r="B93" s="31"/>
+      <c r="C93" s="43"/>
+      <c r="D93" s="29"/>
+      <c r="E93" s="38"/>
+      <c r="F93" s="34">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="94" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A94" s="8"/>
-      <c r="B94" s="25"/>
-      <c r="C94" s="10"/>
-      <c r="D94" s="30"/>
-      <c r="E94" s="86"/>
-      <c r="F94" s="39">
+      <c r="B94" s="24"/>
+      <c r="C94" s="40"/>
+      <c r="D94" s="29"/>
+      <c r="E94" s="38"/>
+      <c r="F94" s="34">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="95" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95" s="8"/>
-      <c r="B95" s="25"/>
-      <c r="C95" s="10"/>
-      <c r="D95" s="30"/>
-      <c r="E95" s="86"/>
-      <c r="F95" s="39">
+      <c r="B95" s="24"/>
+      <c r="C95" s="40"/>
+      <c r="D95" s="29"/>
+      <c r="E95" s="38"/>
+      <c r="F95" s="34">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="96" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A96" s="8"/>
-      <c r="B96" s="25"/>
-      <c r="C96" s="37"/>
-      <c r="D96" s="30"/>
-      <c r="E96" s="86"/>
-      <c r="F96" s="39">
+      <c r="B96" s="24"/>
+      <c r="C96" s="32"/>
+      <c r="D96" s="29"/>
+      <c r="E96" s="38"/>
+      <c r="F96" s="34">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="97" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A97" s="8"/>
-      <c r="B97" s="25"/>
-      <c r="C97" s="10"/>
-      <c r="D97" s="30"/>
-      <c r="E97" s="86"/>
-      <c r="F97" s="39">
+      <c r="B97" s="24"/>
+      <c r="C97" s="40"/>
+      <c r="D97" s="29"/>
+      <c r="E97" s="38"/>
+      <c r="F97" s="34">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="98" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A98" s="8"/>
-      <c r="B98" s="24"/>
-      <c r="C98" s="10"/>
-      <c r="D98" s="30"/>
-      <c r="E98" s="86"/>
-      <c r="F98" s="39">
+      <c r="B98" s="23"/>
+      <c r="C98" s="40"/>
+      <c r="D98" s="29"/>
+      <c r="E98" s="38"/>
+      <c r="F98" s="34">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="99" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A99" s="8"/>
-      <c r="B99" s="24"/>
-      <c r="C99" s="10"/>
-      <c r="D99" s="30"/>
-      <c r="E99" s="86"/>
-      <c r="F99" s="39">
+      <c r="B99" s="23"/>
+      <c r="C99" s="40"/>
+      <c r="D99" s="29"/>
+      <c r="E99" s="38"/>
+      <c r="F99" s="34">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="100" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A100" s="8"/>
-      <c r="B100" s="24"/>
-      <c r="C100" s="10"/>
-      <c r="D100" s="30"/>
-      <c r="E100" s="86"/>
-      <c r="F100" s="39">
+      <c r="B100" s="23"/>
+      <c r="C100" s="40"/>
+      <c r="D100" s="29"/>
+      <c r="E100" s="38"/>
+      <c r="F100" s="34">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="101" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A101" s="8"/>
-      <c r="B101" s="24"/>
-      <c r="C101" s="10"/>
-      <c r="D101" s="30"/>
-      <c r="E101" s="86"/>
-      <c r="F101" s="39">
+      <c r="B101" s="23"/>
+      <c r="C101" s="40"/>
+      <c r="D101" s="29"/>
+      <c r="E101" s="38"/>
+      <c r="F101" s="34">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="102" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A102" s="8"/>
-      <c r="B102" s="24"/>
-      <c r="C102" s="10"/>
-      <c r="D102" s="30"/>
-      <c r="E102" s="86"/>
-      <c r="F102" s="39">
+      <c r="B102" s="23"/>
+      <c r="C102" s="40"/>
+      <c r="D102" s="29"/>
+      <c r="E102" s="38"/>
+      <c r="F102" s="34">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="103" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A103" s="8"/>
-      <c r="B103" s="11"/>
-      <c r="C103" s="37"/>
-      <c r="D103" s="30"/>
-      <c r="E103" s="86"/>
-      <c r="F103" s="39">
+      <c r="B103" s="10"/>
+      <c r="C103" s="32"/>
+      <c r="D103" s="29"/>
+      <c r="E103" s="38"/>
+      <c r="F103" s="34">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="104" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A104" s="8"/>
-      <c r="B104" s="11"/>
-      <c r="C104" s="37"/>
-      <c r="D104" s="30"/>
-      <c r="E104" s="86"/>
-      <c r="F104" s="39">
+      <c r="B104" s="10"/>
+      <c r="C104" s="32"/>
+      <c r="D104" s="29"/>
+      <c r="E104" s="38"/>
+      <c r="F104" s="34">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="105" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A105" s="8"/>
-      <c r="B105" s="11"/>
-      <c r="C105" s="37"/>
-      <c r="D105" s="38"/>
-      <c r="E105" s="86"/>
-      <c r="F105" s="39">
+      <c r="B105" s="10"/>
+      <c r="C105" s="32"/>
+      <c r="D105" s="33"/>
+      <c r="E105" s="38"/>
+      <c r="F105" s="34">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="106" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A106" s="12"/>
-      <c r="B106" s="13"/>
-      <c r="C106" s="14"/>
+      <c r="A106" s="11"/>
+      <c r="B106" s="12"/>
+      <c r="C106" s="13"/>
       <c r="D106" s="73" t="s">
         <v>9</v>
       </c>
@@ -2268,8 +2270,8 @@
       <c r="A110" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B110" s="15"/>
-      <c r="C110" s="21"/>
+      <c r="B110" s="14"/>
+      <c r="C110" s="20"/>
       <c r="D110" s="66"/>
       <c r="E110" s="67"/>
       <c r="F110" s="68"/>
@@ -2278,35 +2280,35 @@
       <c r="A111" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B111" s="15"/>
-      <c r="C111" s="16"/>
+      <c r="B111" s="14"/>
+      <c r="C111" s="15"/>
       <c r="D111" s="69"/>
       <c r="E111" s="69"/>
       <c r="F111" s="70"/>
     </row>
     <row r="112" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A112" s="17" t="s">
+      <c r="A112" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="B112" s="18"/>
-      <c r="C112" s="22"/>
+      <c r="B112" s="17"/>
+      <c r="C112" s="21"/>
       <c r="D112" s="71" t="s">
         <v>15</v>
       </c>
       <c r="E112" s="71"/>
       <c r="F112" s="72"/>
-      <c r="G112" s="43" t="s">
+      <c r="G112" s="37" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A113" s="6"/>
-      <c r="B113" s="19"/>
-      <c r="C113" s="20"/>
-      <c r="D113" s="19"/>
-      <c r="E113" s="19"/>
-      <c r="F113" s="20"/>
-      <c r="G113" s="43" t="s">
+      <c r="B113" s="18"/>
+      <c r="C113" s="19"/>
+      <c r="D113" s="18"/>
+      <c r="E113" s="18"/>
+      <c r="F113" s="19"/>
+      <c r="G113" s="37" t="s">
         <v>24</v>
       </c>
     </row>

--- a/backend/templates/pr-template 3p.xlsx
+++ b/backend/templates/pr-template 3p.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\web-opr\backend\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1090453-91B5-4D7B-8278-4946442D801C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D70B0441-C0B9-4100-96E3-0D94F5DFD50F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -516,6 +516,113 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -533,113 +640,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1052,6 +1052,7 @@
     <col min="4" max="4" width="6" customWidth="1"/>
     <col min="5" max="6" width="13.54296875" customWidth="1"/>
     <col min="7" max="7" width="6.1796875" customWidth="1"/>
+    <col min="12" max="12" width="35.7265625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -1059,26 +1060,26 @@
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
-      <c r="E1" s="52"/>
-      <c r="F1" s="53"/>
+      <c r="E1" s="67"/>
+      <c r="F1" s="68"/>
     </row>
     <row r="2" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="54" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="55"/>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="56"/>
+      <c r="A2" s="69" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="70"/>
+      <c r="C2" s="70"/>
+      <c r="D2" s="70"/>
+      <c r="E2" s="70"/>
+      <c r="F2" s="71"/>
     </row>
     <row r="3" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="57"/>
-      <c r="B3" s="58"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="59"/>
+      <c r="A3" s="72"/>
+      <c r="B3" s="73"/>
+      <c r="C3" s="73"/>
+      <c r="D3" s="73"/>
+      <c r="E3" s="73"/>
+      <c r="F3" s="74"/>
     </row>
     <row r="4" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
@@ -1086,68 +1087,68 @@
       </c>
       <c r="B4" s="25"/>
       <c r="C4" s="26"/>
-      <c r="D4" s="60"/>
-      <c r="E4" s="60"/>
-      <c r="F4" s="61"/>
+      <c r="D4" s="75"/>
+      <c r="E4" s="75"/>
+      <c r="F4" s="76"/>
     </row>
     <row r="5" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="62" t="s">
+      <c r="A5" s="77" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="63"/>
+      <c r="B5" s="78"/>
       <c r="C5" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D5" s="5"/>
-      <c r="E5" s="64" t="s">
+      <c r="E5" s="79" t="s">
         <v>18</v>
       </c>
-      <c r="F5" s="65"/>
+      <c r="F5" s="80"/>
     </row>
     <row r="6" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="46"/>
-      <c r="B6" s="47"/>
+      <c r="A6" s="83"/>
+      <c r="B6" s="84"/>
       <c r="C6" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D6" s="7"/>
-      <c r="E6" s="44" t="s">
+      <c r="E6" s="81" t="s">
         <v>20</v>
       </c>
-      <c r="F6" s="45"/>
+      <c r="F6" s="82"/>
     </row>
     <row r="7" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="48" t="s">
+      <c r="A7" s="85" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="50" t="s">
+      <c r="B7" s="52" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="50" t="s">
+      <c r="C7" s="52" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="50" t="s">
+      <c r="D7" s="52" t="s">
         <v>6</v>
       </c>
-      <c r="E7" s="50" t="s">
+      <c r="E7" s="52" t="s">
         <v>7</v>
       </c>
-      <c r="F7" s="50" t="s">
+      <c r="F7" s="52" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="49"/>
-      <c r="B8" s="51"/>
-      <c r="C8" s="51"/>
-      <c r="D8" s="51"/>
-      <c r="E8" s="51"/>
-      <c r="F8" s="51"/>
+      <c r="A8" s="86"/>
+      <c r="B8" s="53"/>
+      <c r="C8" s="53"/>
+      <c r="D8" s="53"/>
+      <c r="E8" s="53"/>
+      <c r="F8" s="53"/>
     </row>
     <row r="9" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="36"/>
       <c r="B9" s="27"/>
-      <c r="C9" s="86"/>
+      <c r="C9" s="44"/>
       <c r="D9" s="35"/>
       <c r="E9" s="38"/>
       <c r="F9" s="34">
@@ -1158,7 +1159,7 @@
     <row r="10" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="36"/>
       <c r="B10" s="27"/>
-      <c r="C10" s="86"/>
+      <c r="C10" s="44"/>
       <c r="D10" s="35"/>
       <c r="E10" s="38"/>
       <c r="F10" s="34">
@@ -1169,7 +1170,7 @@
     <row r="11" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="36"/>
       <c r="B11" s="27"/>
-      <c r="C11" s="86"/>
+      <c r="C11" s="44"/>
       <c r="D11" s="35"/>
       <c r="E11" s="38"/>
       <c r="F11" s="34">
@@ -1180,7 +1181,7 @@
     <row r="12" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="36"/>
       <c r="B12" s="27"/>
-      <c r="C12" s="86"/>
+      <c r="C12" s="44"/>
       <c r="D12" s="35"/>
       <c r="E12" s="38"/>
       <c r="F12" s="34">
@@ -1191,7 +1192,7 @@
     <row r="13" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="36"/>
       <c r="B13" s="27"/>
-      <c r="C13" s="86"/>
+      <c r="C13" s="44"/>
       <c r="D13" s="35"/>
       <c r="E13" s="38"/>
       <c r="F13" s="34">
@@ -1202,7 +1203,7 @@
     <row r="14" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="36"/>
       <c r="B14" s="27"/>
-      <c r="C14" s="86"/>
+      <c r="C14" s="44"/>
       <c r="D14" s="35"/>
       <c r="E14" s="38"/>
       <c r="F14" s="34">
@@ -1213,7 +1214,7 @@
     <row r="15" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="36"/>
       <c r="B15" s="27"/>
-      <c r="C15" s="86"/>
+      <c r="C15" s="44"/>
       <c r="D15" s="35"/>
       <c r="E15" s="38"/>
       <c r="F15" s="34">
@@ -1224,7 +1225,7 @@
     <row r="16" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="36"/>
       <c r="B16" s="27"/>
-      <c r="C16" s="86"/>
+      <c r="C16" s="44"/>
       <c r="D16" s="35"/>
       <c r="E16" s="38"/>
       <c r="F16" s="34">
@@ -1235,7 +1236,7 @@
     <row r="17" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="36"/>
       <c r="B17" s="27"/>
-      <c r="C17" s="86"/>
+      <c r="C17" s="44"/>
       <c r="D17" s="35"/>
       <c r="E17" s="38"/>
       <c r="F17" s="34">
@@ -1246,7 +1247,7 @@
     <row r="18" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="36"/>
       <c r="B18" s="27"/>
-      <c r="C18" s="86"/>
+      <c r="C18" s="44"/>
       <c r="D18" s="35"/>
       <c r="E18" s="38"/>
       <c r="F18" s="34">
@@ -1257,7 +1258,7 @@
     <row r="19" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="36"/>
       <c r="B19" s="27"/>
-      <c r="C19" s="86"/>
+      <c r="C19" s="44"/>
       <c r="D19" s="35"/>
       <c r="E19" s="38"/>
       <c r="F19" s="34">
@@ -1268,7 +1269,7 @@
     <row r="20" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="36"/>
       <c r="B20" s="27"/>
-      <c r="C20" s="86"/>
+      <c r="C20" s="44"/>
       <c r="D20" s="35"/>
       <c r="E20" s="38"/>
       <c r="F20" s="34">
@@ -1279,7 +1280,7 @@
     <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="36"/>
       <c r="B21" s="27"/>
-      <c r="C21" s="86"/>
+      <c r="C21" s="44"/>
       <c r="D21" s="35"/>
       <c r="E21" s="38"/>
       <c r="F21" s="34">
@@ -1290,7 +1291,7 @@
     <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="36"/>
       <c r="B22" s="27"/>
-      <c r="C22" s="86"/>
+      <c r="C22" s="44"/>
       <c r="D22" s="35"/>
       <c r="E22" s="38"/>
       <c r="F22" s="34">
@@ -1301,7 +1302,7 @@
     <row r="23" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="36"/>
       <c r="B23" s="27"/>
-      <c r="C23" s="86"/>
+      <c r="C23" s="44"/>
       <c r="D23" s="35"/>
       <c r="E23" s="38"/>
       <c r="F23" s="34">
@@ -1312,7 +1313,7 @@
     <row r="24" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="36"/>
       <c r="B24" s="27"/>
-      <c r="C24" s="86"/>
+      <c r="C24" s="44"/>
       <c r="D24" s="35"/>
       <c r="E24" s="38"/>
       <c r="F24" s="34">
@@ -1323,7 +1324,7 @@
     <row r="25" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="36"/>
       <c r="B25" s="27"/>
-      <c r="C25" s="86"/>
+      <c r="C25" s="44"/>
       <c r="D25" s="35"/>
       <c r="E25" s="38"/>
       <c r="F25" s="34">
@@ -1334,7 +1335,7 @@
     <row r="26" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="36"/>
       <c r="B26" s="27"/>
-      <c r="C26" s="86"/>
+      <c r="C26" s="44"/>
       <c r="D26" s="35"/>
       <c r="E26" s="38"/>
       <c r="F26" s="34">
@@ -1345,7 +1346,7 @@
     <row r="27" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="36"/>
       <c r="B27" s="27"/>
-      <c r="C27" s="86"/>
+      <c r="C27" s="44"/>
       <c r="D27" s="35"/>
       <c r="E27" s="38"/>
       <c r="F27" s="34">
@@ -1356,7 +1357,7 @@
     <row r="28" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="36"/>
       <c r="B28" s="27"/>
-      <c r="C28" s="86"/>
+      <c r="C28" s="44"/>
       <c r="D28" s="35"/>
       <c r="E28" s="38"/>
       <c r="F28" s="34">
@@ -1367,7 +1368,7 @@
     <row r="29" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="36"/>
       <c r="B29" s="27"/>
-      <c r="C29" s="86"/>
+      <c r="C29" s="44"/>
       <c r="D29" s="35"/>
       <c r="E29" s="38"/>
       <c r="F29" s="34">
@@ -1378,7 +1379,7 @@
     <row r="30" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="36"/>
       <c r="B30" s="27"/>
-      <c r="C30" s="86"/>
+      <c r="C30" s="44"/>
       <c r="D30" s="35"/>
       <c r="E30" s="38"/>
       <c r="F30" s="34">
@@ -1389,7 +1390,7 @@
     <row r="31" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="36"/>
       <c r="B31" s="27"/>
-      <c r="C31" s="86"/>
+      <c r="C31" s="44"/>
       <c r="D31" s="35"/>
       <c r="E31" s="38"/>
       <c r="F31" s="34">
@@ -1400,7 +1401,7 @@
     <row r="32" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="36"/>
       <c r="B32" s="27"/>
-      <c r="C32" s="86"/>
+      <c r="C32" s="44"/>
       <c r="D32" s="35"/>
       <c r="E32" s="38"/>
       <c r="F32" s="34">
@@ -1411,7 +1412,7 @@
     <row r="33" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="36"/>
       <c r="B33" s="27"/>
-      <c r="C33" s="86"/>
+      <c r="C33" s="44"/>
       <c r="D33" s="35"/>
       <c r="E33" s="38"/>
       <c r="F33" s="34">
@@ -1422,7 +1423,7 @@
     <row r="34" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="36"/>
       <c r="B34" s="27"/>
-      <c r="C34" s="86"/>
+      <c r="C34" s="44"/>
       <c r="D34" s="35"/>
       <c r="E34" s="38"/>
       <c r="F34" s="34">
@@ -1433,7 +1434,7 @@
     <row r="35" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="36"/>
       <c r="B35" s="27"/>
-      <c r="C35" s="86"/>
+      <c r="C35" s="44"/>
       <c r="D35" s="35"/>
       <c r="E35" s="38"/>
       <c r="F35" s="34">
@@ -1444,7 +1445,7 @@
     <row r="36" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="36"/>
       <c r="B36" s="27"/>
-      <c r="C36" s="86"/>
+      <c r="C36" s="44"/>
       <c r="D36" s="35"/>
       <c r="E36" s="38"/>
       <c r="F36" s="34">
@@ -1455,7 +1456,7 @@
     <row r="37" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="36"/>
       <c r="B37" s="27"/>
-      <c r="C37" s="86"/>
+      <c r="C37" s="44"/>
       <c r="D37" s="35"/>
       <c r="E37" s="38"/>
       <c r="F37" s="34">
@@ -1466,7 +1467,7 @@
     <row r="38" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="36"/>
       <c r="B38" s="27"/>
-      <c r="C38" s="86"/>
+      <c r="C38" s="44"/>
       <c r="D38" s="35"/>
       <c r="E38" s="38"/>
       <c r="F38" s="34">
@@ -1477,7 +1478,7 @@
     <row r="39" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="36"/>
       <c r="B39" s="27"/>
-      <c r="C39" s="86"/>
+      <c r="C39" s="44"/>
       <c r="D39" s="35"/>
       <c r="E39" s="38"/>
       <c r="F39" s="34">
@@ -1491,7 +1492,7 @@
     <row r="40" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="36"/>
       <c r="B40" s="27"/>
-      <c r="C40" s="86"/>
+      <c r="C40" s="44"/>
       <c r="D40" s="35"/>
       <c r="E40" s="38"/>
       <c r="F40" s="34">
@@ -1505,7 +1506,7 @@
     <row r="41" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="36"/>
       <c r="B41" s="27"/>
-      <c r="C41" s="86"/>
+      <c r="C41" s="44"/>
       <c r="D41" s="35"/>
       <c r="E41" s="38"/>
       <c r="F41" s="34">
@@ -1516,7 +1517,7 @@
     <row r="42" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="36"/>
       <c r="B42" s="27"/>
-      <c r="C42" s="86"/>
+      <c r="C42" s="44"/>
       <c r="D42" s="35"/>
       <c r="E42" s="38"/>
       <c r="F42" s="34">
@@ -1527,7 +1528,7 @@
     <row r="43" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="36"/>
       <c r="B43" s="27"/>
-      <c r="C43" s="86"/>
+      <c r="C43" s="44"/>
       <c r="D43" s="35"/>
       <c r="E43" s="38"/>
       <c r="F43" s="34">
@@ -1538,7 +1539,7 @@
     <row r="44" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="36"/>
       <c r="B44" s="27"/>
-      <c r="C44" s="86"/>
+      <c r="C44" s="44"/>
       <c r="D44" s="35"/>
       <c r="E44" s="38"/>
       <c r="F44" s="34">
@@ -1549,7 +1550,7 @@
     <row r="45" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="36"/>
       <c r="B45" s="27"/>
-      <c r="C45" s="86"/>
+      <c r="C45" s="44"/>
       <c r="D45" s="35"/>
       <c r="E45" s="38"/>
       <c r="F45" s="34">
@@ -1560,7 +1561,7 @@
     <row r="46" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="36"/>
       <c r="B46" s="27"/>
-      <c r="C46" s="86"/>
+      <c r="C46" s="44"/>
       <c r="D46" s="35"/>
       <c r="E46" s="38"/>
       <c r="F46" s="34">
@@ -1571,7 +1572,7 @@
     <row r="47" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="36"/>
       <c r="B47" s="27"/>
-      <c r="C47" s="86"/>
+      <c r="C47" s="44"/>
       <c r="D47" s="35"/>
       <c r="E47" s="38"/>
       <c r="F47" s="34">
@@ -1582,7 +1583,7 @@
     <row r="48" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="36"/>
       <c r="B48" s="27"/>
-      <c r="C48" s="86"/>
+      <c r="C48" s="44"/>
       <c r="D48" s="35"/>
       <c r="E48" s="38"/>
       <c r="F48" s="34">
@@ -1593,7 +1594,7 @@
     <row r="49" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="36"/>
       <c r="B49" s="27"/>
-      <c r="C49" s="86"/>
+      <c r="C49" s="44"/>
       <c r="D49" s="35"/>
       <c r="E49" s="38"/>
       <c r="F49" s="34">
@@ -1604,7 +1605,7 @@
     <row r="50" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="36"/>
       <c r="B50" s="27"/>
-      <c r="C50" s="86"/>
+      <c r="C50" s="44"/>
       <c r="D50" s="35"/>
       <c r="E50" s="38"/>
       <c r="F50" s="34">
@@ -1615,7 +1616,7 @@
     <row r="51" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="36"/>
       <c r="B51" s="27"/>
-      <c r="C51" s="86"/>
+      <c r="C51" s="44"/>
       <c r="D51" s="35"/>
       <c r="E51" s="38"/>
       <c r="F51" s="34">
@@ -1626,7 +1627,7 @@
     <row r="52" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="36"/>
       <c r="B52" s="27"/>
-      <c r="C52" s="86"/>
+      <c r="C52" s="44"/>
       <c r="D52" s="35"/>
       <c r="E52" s="38"/>
       <c r="F52" s="34">
@@ -1637,7 +1638,7 @@
     <row r="53" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="36"/>
       <c r="B53" s="27"/>
-      <c r="C53" s="86"/>
+      <c r="C53" s="44"/>
       <c r="D53" s="35"/>
       <c r="E53" s="38"/>
       <c r="F53" s="34">
@@ -1648,7 +1649,7 @@
     <row r="54" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="36"/>
       <c r="B54" s="27"/>
-      <c r="C54" s="86"/>
+      <c r="C54" s="44"/>
       <c r="D54" s="35"/>
       <c r="E54" s="38"/>
       <c r="F54" s="34">
@@ -1659,7 +1660,7 @@
     <row r="55" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="36"/>
       <c r="B55" s="27"/>
-      <c r="C55" s="86"/>
+      <c r="C55" s="44"/>
       <c r="D55" s="35"/>
       <c r="E55" s="38"/>
       <c r="F55" s="34">
@@ -1670,7 +1671,7 @@
     <row r="56" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="36"/>
       <c r="B56" s="27"/>
-      <c r="C56" s="86"/>
+      <c r="C56" s="44"/>
       <c r="D56" s="35"/>
       <c r="E56" s="38"/>
       <c r="F56" s="34">
@@ -1681,7 +1682,7 @@
     <row r="57" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="36"/>
       <c r="B57" s="27"/>
-      <c r="C57" s="86"/>
+      <c r="C57" s="44"/>
       <c r="D57" s="35"/>
       <c r="E57" s="38"/>
       <c r="F57" s="34">
@@ -1692,7 +1693,7 @@
     <row r="58" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="36"/>
       <c r="B58" s="27"/>
-      <c r="C58" s="86"/>
+      <c r="C58" s="44"/>
       <c r="D58" s="35"/>
       <c r="E58" s="38"/>
       <c r="F58" s="34">
@@ -1703,7 +1704,7 @@
     <row r="59" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="36"/>
       <c r="B59" s="27"/>
-      <c r="C59" s="86"/>
+      <c r="C59" s="44"/>
       <c r="D59" s="35"/>
       <c r="E59" s="38"/>
       <c r="F59" s="34">
@@ -1714,7 +1715,7 @@
     <row r="60" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="36"/>
       <c r="B60" s="27"/>
-      <c r="C60" s="86"/>
+      <c r="C60" s="44"/>
       <c r="D60" s="35"/>
       <c r="E60" s="38"/>
       <c r="F60" s="34">
@@ -1725,7 +1726,7 @@
     <row r="61" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="36"/>
       <c r="B61" s="27"/>
-      <c r="C61" s="86"/>
+      <c r="C61" s="44"/>
       <c r="D61" s="35"/>
       <c r="E61" s="38"/>
       <c r="F61" s="34">
@@ -1736,7 +1737,7 @@
     <row r="62" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="36"/>
       <c r="B62" s="27"/>
-      <c r="C62" s="86"/>
+      <c r="C62" s="44"/>
       <c r="D62" s="35"/>
       <c r="E62" s="38"/>
       <c r="F62" s="34">
@@ -1747,7 +1748,7 @@
     <row r="63" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="36"/>
       <c r="B63" s="27"/>
-      <c r="C63" s="86"/>
+      <c r="C63" s="44"/>
       <c r="D63" s="35"/>
       <c r="E63" s="38"/>
       <c r="F63" s="34">
@@ -1758,7 +1759,7 @@
     <row r="64" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="36"/>
       <c r="B64" s="27"/>
-      <c r="C64" s="86"/>
+      <c r="C64" s="44"/>
       <c r="D64" s="35"/>
       <c r="E64" s="38"/>
       <c r="F64" s="34">
@@ -1769,7 +1770,7 @@
     <row r="65" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="36"/>
       <c r="B65" s="27"/>
-      <c r="C65" s="86"/>
+      <c r="C65" s="44"/>
       <c r="D65" s="35"/>
       <c r="E65" s="38"/>
       <c r="F65" s="34">
@@ -1780,7 +1781,7 @@
     <row r="66" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="36"/>
       <c r="B66" s="27"/>
-      <c r="C66" s="86"/>
+      <c r="C66" s="44"/>
       <c r="D66" s="35"/>
       <c r="E66" s="38"/>
       <c r="F66" s="34">
@@ -1791,7 +1792,7 @@
     <row r="67" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="36"/>
       <c r="B67" s="27"/>
-      <c r="C67" s="86"/>
+      <c r="C67" s="44"/>
       <c r="D67" s="35"/>
       <c r="E67" s="38"/>
       <c r="F67" s="34">
@@ -1802,7 +1803,7 @@
     <row r="68" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="36"/>
       <c r="B68" s="27"/>
-      <c r="C68" s="86"/>
+      <c r="C68" s="44"/>
       <c r="D68" s="35"/>
       <c r="E68" s="38"/>
       <c r="F68" s="34">
@@ -1813,7 +1814,7 @@
     <row r="69" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="36"/>
       <c r="B69" s="27"/>
-      <c r="C69" s="86"/>
+      <c r="C69" s="44"/>
       <c r="D69" s="35"/>
       <c r="E69" s="38"/>
       <c r="F69" s="34">
@@ -1824,7 +1825,7 @@
     <row r="70" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" s="36"/>
       <c r="B70" s="27"/>
-      <c r="C70" s="86"/>
+      <c r="C70" s="44"/>
       <c r="D70" s="35"/>
       <c r="E70" s="38"/>
       <c r="F70" s="34">
@@ -1835,7 +1836,7 @@
     <row r="71" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" s="36"/>
       <c r="B71" s="27"/>
-      <c r="C71" s="86"/>
+      <c r="C71" s="44"/>
       <c r="D71" s="35"/>
       <c r="E71" s="38"/>
       <c r="F71" s="34">
@@ -1846,7 +1847,7 @@
     <row r="72" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="36"/>
       <c r="B72" s="27"/>
-      <c r="C72" s="86"/>
+      <c r="C72" s="44"/>
       <c r="D72" s="35"/>
       <c r="E72" s="38"/>
       <c r="F72" s="34">
@@ -1857,7 +1858,7 @@
     <row r="73" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="36"/>
       <c r="B73" s="27"/>
-      <c r="C73" s="86"/>
+      <c r="C73" s="44"/>
       <c r="D73" s="35"/>
       <c r="E73" s="38"/>
       <c r="F73" s="34">
@@ -1868,7 +1869,7 @@
     <row r="74" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="36"/>
       <c r="B74" s="27"/>
-      <c r="C74" s="86"/>
+      <c r="C74" s="44"/>
       <c r="D74" s="35"/>
       <c r="E74" s="38"/>
       <c r="F74" s="34">
@@ -1879,7 +1880,7 @@
     <row r="75" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="36"/>
       <c r="B75" s="27"/>
-      <c r="C75" s="86"/>
+      <c r="C75" s="44"/>
       <c r="D75" s="35"/>
       <c r="E75" s="38"/>
       <c r="F75" s="34">
@@ -1890,7 +1891,7 @@
     <row r="76" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="36"/>
       <c r="B76" s="27"/>
-      <c r="C76" s="86"/>
+      <c r="C76" s="44"/>
       <c r="D76" s="35"/>
       <c r="E76" s="38"/>
       <c r="F76" s="34">
@@ -1901,7 +1902,7 @@
     <row r="77" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="36"/>
       <c r="B77" s="27"/>
-      <c r="C77" s="86"/>
+      <c r="C77" s="44"/>
       <c r="D77" s="35"/>
       <c r="E77" s="38"/>
       <c r="F77" s="34">
@@ -1912,7 +1913,7 @@
     <row r="78" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="36"/>
       <c r="B78" s="27"/>
-      <c r="C78" s="86"/>
+      <c r="C78" s="44"/>
       <c r="D78" s="35"/>
       <c r="E78" s="38"/>
       <c r="F78" s="34">
@@ -1923,7 +1924,7 @@
     <row r="79" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="36"/>
       <c r="B79" s="27"/>
-      <c r="C79" s="86"/>
+      <c r="C79" s="44"/>
       <c r="D79" s="35"/>
       <c r="E79" s="38"/>
       <c r="F79" s="34">
@@ -2227,44 +2228,44 @@
       <c r="A106" s="11"/>
       <c r="B106" s="12"/>
       <c r="C106" s="13"/>
-      <c r="D106" s="73" t="s">
+      <c r="D106" s="54" t="s">
         <v>9</v>
       </c>
-      <c r="E106" s="74"/>
+      <c r="E106" s="55"/>
       <c r="F106" s="9">
         <f>SUM(F9:F105)</f>
         <v>0</v>
       </c>
     </row>
     <row r="107" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A107" s="83" t="s">
+      <c r="A107" s="64" t="s">
         <v>16</v>
       </c>
-      <c r="B107" s="84"/>
-      <c r="C107" s="84"/>
-      <c r="D107" s="84"/>
-      <c r="E107" s="84"/>
-      <c r="F107" s="85"/>
+      <c r="B107" s="65"/>
+      <c r="C107" s="65"/>
+      <c r="D107" s="65"/>
+      <c r="E107" s="65"/>
+      <c r="F107" s="66"/>
     </row>
     <row r="108" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A108" s="75"/>
-      <c r="B108" s="76"/>
-      <c r="C108" s="76"/>
-      <c r="D108" s="76"/>
-      <c r="E108" s="76"/>
-      <c r="F108" s="77"/>
+      <c r="A108" s="56"/>
+      <c r="B108" s="57"/>
+      <c r="C108" s="57"/>
+      <c r="D108" s="57"/>
+      <c r="E108" s="57"/>
+      <c r="F108" s="58"/>
     </row>
     <row r="109" spans="1:7" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A109" s="78" t="s">
+      <c r="A109" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="B109" s="79"/>
-      <c r="C109" s="80"/>
-      <c r="D109" s="81" t="s">
+      <c r="B109" s="60"/>
+      <c r="C109" s="61"/>
+      <c r="D109" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="E109" s="81"/>
-      <c r="F109" s="82"/>
+      <c r="E109" s="62"/>
+      <c r="F109" s="63"/>
     </row>
     <row r="110" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A110" s="3" t="s">
@@ -2272,9 +2273,9 @@
       </c>
       <c r="B110" s="14"/>
       <c r="C110" s="20"/>
-      <c r="D110" s="66"/>
-      <c r="E110" s="67"/>
-      <c r="F110" s="68"/>
+      <c r="D110" s="45"/>
+      <c r="E110" s="46"/>
+      <c r="F110" s="47"/>
     </row>
     <row r="111" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A111" s="3" t="s">
@@ -2282,9 +2283,9 @@
       </c>
       <c r="B111" s="14"/>
       <c r="C111" s="15"/>
-      <c r="D111" s="69"/>
-      <c r="E111" s="69"/>
-      <c r="F111" s="70"/>
+      <c r="D111" s="48"/>
+      <c r="E111" s="48"/>
+      <c r="F111" s="49"/>
     </row>
     <row r="112" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A112" s="16" t="s">
@@ -2292,11 +2293,11 @@
       </c>
       <c r="B112" s="17"/>
       <c r="C112" s="21"/>
-      <c r="D112" s="71" t="s">
+      <c r="D112" s="50" t="s">
         <v>15</v>
       </c>
-      <c r="E112" s="71"/>
-      <c r="F112" s="72"/>
+      <c r="E112" s="50"/>
+      <c r="F112" s="51"/>
       <c r="G112" s="37" t="s">
         <v>21</v>
       </c>
@@ -2317,6 +2318,18 @@
     <sortCondition ref="K6:K93"/>
   </sortState>
   <mergeCells count="23">
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="D4:F4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="E5:F5"/>
     <mergeCell ref="D110:F110"/>
     <mergeCell ref="D111:F111"/>
     <mergeCell ref="D112:F112"/>
@@ -2328,18 +2341,6 @@
     <mergeCell ref="E7:E8"/>
     <mergeCell ref="A107:B107"/>
     <mergeCell ref="C107:F107"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="D4:F4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="D7:D8"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="1.7716535433070868" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="91" fitToHeight="0" orientation="portrait" r:id="rId1"/>

--- a/backend/templates/pr-template 3p.xlsx
+++ b/backend/templates/pr-template 3p.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\web-opr\backend\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BC61CCE-6AB2-4A82-9352-4207CFF5B483}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCC08D0E-CC6B-44B4-8617-81C5BBE76190}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -508,6 +508,83 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
     </xf>
@@ -529,12 +606,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -573,77 +644,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1047,7 +1047,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G106"/>
+  <dimension ref="A1:G123"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="7.54296875" customWidth="1"/>
@@ -1064,26 +1064,26 @@
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="66"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="57"/>
     </row>
     <row r="2" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="67" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="68"/>
-      <c r="C2" s="68"/>
-      <c r="D2" s="68"/>
-      <c r="E2" s="68"/>
-      <c r="F2" s="69"/>
+      <c r="A2" s="58" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="59"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="60"/>
     </row>
     <row r="3" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="70"/>
-      <c r="B3" s="71"/>
-      <c r="C3" s="71"/>
-      <c r="D3" s="71"/>
-      <c r="E3" s="71"/>
-      <c r="F3" s="72"/>
+      <c r="A3" s="61"/>
+      <c r="B3" s="62"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="63"/>
     </row>
     <row r="4" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
@@ -1091,63 +1091,63 @@
       </c>
       <c r="B4" s="24"/>
       <c r="C4" s="25"/>
-      <c r="D4" s="73"/>
-      <c r="E4" s="73"/>
-      <c r="F4" s="74"/>
+      <c r="D4" s="64"/>
+      <c r="E4" s="64"/>
+      <c r="F4" s="65"/>
     </row>
     <row r="5" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="75" t="s">
+      <c r="A5" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="76"/>
+      <c r="B5" s="67"/>
       <c r="C5" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D5" s="5"/>
-      <c r="E5" s="77" t="s">
+      <c r="E5" s="68" t="s">
         <v>18</v>
       </c>
-      <c r="F5" s="78"/>
+      <c r="F5" s="69"/>
     </row>
     <row r="6" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="81"/>
-      <c r="B6" s="82"/>
+      <c r="A6" s="50"/>
+      <c r="B6" s="51"/>
       <c r="C6" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D6" s="7"/>
-      <c r="E6" s="79" t="s">
+      <c r="E6" s="48" t="s">
         <v>20</v>
       </c>
-      <c r="F6" s="80"/>
+      <c r="F6" s="49"/>
     </row>
     <row r="7" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="83" t="s">
+      <c r="A7" s="52" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="50" t="s">
+      <c r="B7" s="54" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="50" t="s">
+      <c r="C7" s="54" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="50" t="s">
+      <c r="D7" s="54" t="s">
         <v>6</v>
       </c>
-      <c r="E7" s="50" t="s">
+      <c r="E7" s="54" t="s">
         <v>7</v>
       </c>
-      <c r="F7" s="50" t="s">
+      <c r="F7" s="54" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="84"/>
-      <c r="B8" s="51"/>
-      <c r="C8" s="51"/>
-      <c r="D8" s="51"/>
-      <c r="E8" s="51"/>
-      <c r="F8" s="51"/>
+      <c r="A8" s="53"/>
+      <c r="B8" s="55"/>
+      <c r="C8" s="55"/>
+      <c r="D8" s="55"/>
+      <c r="E8" s="55"/>
+      <c r="F8" s="55"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="34"/>
@@ -1574,11 +1574,11 @@
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A47" s="85"/>
-      <c r="B47" s="86"/>
-      <c r="C47" s="87"/>
-      <c r="D47" s="88"/>
-      <c r="E47" s="89"/>
+      <c r="A47" s="43"/>
+      <c r="B47" s="44"/>
+      <c r="C47" s="45"/>
+      <c r="D47" s="46"/>
+      <c r="E47" s="47"/>
       <c r="F47" s="32">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -1943,7 +1943,7 @@
       <c r="D80" s="27"/>
       <c r="E80" s="36"/>
       <c r="F80" s="32">
-        <f t="shared" ref="F80:F98" si="2">D80*E80</f>
+        <f t="shared" ref="F80:F115" si="2">D80*E80</f>
         <v>0</v>
       </c>
     </row>
@@ -2101,142 +2101,344 @@
       <c r="B94" s="23"/>
       <c r="C94" s="38"/>
       <c r="D94" s="21"/>
-      <c r="E94" s="89"/>
+      <c r="E94" s="47"/>
       <c r="F94" s="32">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
+      <c r="G94" s="35"/>
     </row>
     <row r="95" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A95" s="8"/>
-      <c r="B95" s="23"/>
-      <c r="C95" s="38"/>
+      <c r="B95" s="30"/>
+      <c r="C95" s="41"/>
       <c r="D95" s="28"/>
       <c r="E95" s="36"/>
       <c r="F95" s="32">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
+      <c r="G95" s="35"/>
     </row>
     <row r="96" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A96" s="8"/>
-      <c r="B96" s="23"/>
-      <c r="C96" s="31"/>
+      <c r="B96" s="30"/>
+      <c r="C96" s="41"/>
       <c r="D96" s="28"/>
       <c r="E96" s="36"/>
       <c r="F96" s="32">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
+      <c r="G96" s="35"/>
     </row>
     <row r="97" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A97" s="8"/>
-      <c r="B97" s="23"/>
-      <c r="C97" s="38"/>
+      <c r="B97" s="30"/>
+      <c r="C97" s="41"/>
       <c r="D97" s="28"/>
       <c r="E97" s="36"/>
       <c r="F97" s="32">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
+      <c r="G97" s="35"/>
     </row>
     <row r="98" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A98" s="8"/>
-      <c r="B98" s="22"/>
-      <c r="C98" s="38"/>
+      <c r="B98" s="30"/>
+      <c r="C98" s="41"/>
       <c r="D98" s="28"/>
       <c r="E98" s="36"/>
       <c r="F98" s="32">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A99" s="10"/>
-      <c r="B99" s="11"/>
-      <c r="C99" s="12"/>
-      <c r="D99" s="52" t="s">
+      <c r="G98" s="35"/>
+    </row>
+    <row r="99" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A99" s="8"/>
+      <c r="B99" s="30"/>
+      <c r="C99" s="41"/>
+      <c r="D99" s="28"/>
+      <c r="E99" s="36"/>
+      <c r="F99" s="32">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G99" s="35"/>
+    </row>
+    <row r="100" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A100" s="8"/>
+      <c r="B100" s="30"/>
+      <c r="C100" s="41"/>
+      <c r="D100" s="28"/>
+      <c r="E100" s="36"/>
+      <c r="F100" s="32">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G100" s="35"/>
+    </row>
+    <row r="101" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A101" s="8"/>
+      <c r="B101" s="30"/>
+      <c r="C101" s="41"/>
+      <c r="D101" s="28"/>
+      <c r="E101" s="36"/>
+      <c r="F101" s="32">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G101" s="35"/>
+    </row>
+    <row r="102" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A102" s="8"/>
+      <c r="B102" s="30"/>
+      <c r="C102" s="41"/>
+      <c r="D102" s="28"/>
+      <c r="E102" s="36"/>
+      <c r="F102" s="32">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G102" s="35"/>
+    </row>
+    <row r="103" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A103" s="8"/>
+      <c r="B103" s="30"/>
+      <c r="C103" s="41"/>
+      <c r="D103" s="28"/>
+      <c r="E103" s="36"/>
+      <c r="F103" s="32">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G103" s="35"/>
+    </row>
+    <row r="104" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A104" s="8"/>
+      <c r="B104" s="30"/>
+      <c r="C104" s="41"/>
+      <c r="D104" s="28"/>
+      <c r="E104" s="36"/>
+      <c r="F104" s="32">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G104" s="35"/>
+    </row>
+    <row r="105" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A105" s="8"/>
+      <c r="B105" s="30"/>
+      <c r="C105" s="41"/>
+      <c r="D105" s="28"/>
+      <c r="E105" s="36"/>
+      <c r="F105" s="32">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G105" s="35"/>
+    </row>
+    <row r="106" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A106" s="8"/>
+      <c r="B106" s="30"/>
+      <c r="C106" s="41"/>
+      <c r="D106" s="28"/>
+      <c r="E106" s="36"/>
+      <c r="F106" s="32">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G106" s="35"/>
+    </row>
+    <row r="107" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A107" s="8"/>
+      <c r="B107" s="30"/>
+      <c r="C107" s="41"/>
+      <c r="D107" s="28"/>
+      <c r="E107" s="36"/>
+      <c r="F107" s="32">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G107" s="35"/>
+    </row>
+    <row r="108" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A108" s="8"/>
+      <c r="B108" s="30"/>
+      <c r="C108" s="41"/>
+      <c r="D108" s="28"/>
+      <c r="E108" s="36"/>
+      <c r="F108" s="32">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G108" s="35"/>
+    </row>
+    <row r="109" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A109" s="8"/>
+      <c r="B109" s="23"/>
+      <c r="C109" s="38"/>
+      <c r="D109" s="21"/>
+      <c r="E109" s="47"/>
+      <c r="F109" s="32">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A110" s="8"/>
+      <c r="B110" s="23"/>
+      <c r="C110" s="38"/>
+      <c r="D110" s="28"/>
+      <c r="E110" s="36"/>
+      <c r="F110" s="32">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A111" s="8"/>
+      <c r="B111" s="23"/>
+      <c r="C111" s="31"/>
+      <c r="D111" s="28"/>
+      <c r="E111" s="36"/>
+      <c r="F111" s="32">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A112" s="8"/>
+      <c r="B112" s="23"/>
+      <c r="C112" s="31"/>
+      <c r="D112" s="28"/>
+      <c r="E112" s="36"/>
+      <c r="F112" s="32">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A113" s="8"/>
+      <c r="B113" s="23"/>
+      <c r="C113" s="31"/>
+      <c r="D113" s="28"/>
+      <c r="E113" s="36"/>
+      <c r="F113" s="32">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A114" s="8"/>
+      <c r="B114" s="23"/>
+      <c r="C114" s="38"/>
+      <c r="D114" s="28"/>
+      <c r="E114" s="36"/>
+      <c r="F114" s="32">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A115" s="8"/>
+      <c r="B115" s="22"/>
+      <c r="C115" s="38"/>
+      <c r="D115" s="28"/>
+      <c r="E115" s="36"/>
+      <c r="F115" s="32">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A116" s="10"/>
+      <c r="B116" s="11"/>
+      <c r="C116" s="12"/>
+      <c r="D116" s="77" t="s">
         <v>9</v>
       </c>
-      <c r="E99" s="53"/>
-      <c r="F99" s="9">
-        <f>SUM(F9:F98)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A100" s="62" t="s">
+      <c r="E116" s="78"/>
+      <c r="F116" s="9">
+        <f>SUM(F9:F115)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A117" s="87" t="s">
         <v>16</v>
       </c>
-      <c r="B100" s="63"/>
-      <c r="C100" s="63"/>
-      <c r="D100" s="63"/>
-      <c r="E100" s="63"/>
-      <c r="F100" s="64"/>
-    </row>
-    <row r="101" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A101" s="54"/>
-      <c r="B101" s="55"/>
-      <c r="C101" s="55"/>
-      <c r="D101" s="55"/>
-      <c r="E101" s="55"/>
-      <c r="F101" s="56"/>
-    </row>
-    <row r="102" spans="1:7" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A102" s="57" t="s">
+      <c r="B117" s="88"/>
+      <c r="C117" s="88"/>
+      <c r="D117" s="88"/>
+      <c r="E117" s="88"/>
+      <c r="F117" s="89"/>
+    </row>
+    <row r="118" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A118" s="79"/>
+      <c r="B118" s="80"/>
+      <c r="C118" s="80"/>
+      <c r="D118" s="80"/>
+      <c r="E118" s="80"/>
+      <c r="F118" s="81"/>
+    </row>
+    <row r="119" spans="1:7" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A119" s="82" t="s">
         <v>10</v>
       </c>
-      <c r="B102" s="58"/>
-      <c r="C102" s="59"/>
-      <c r="D102" s="60" t="s">
+      <c r="B119" s="83"/>
+      <c r="C119" s="84"/>
+      <c r="D119" s="85" t="s">
         <v>11</v>
       </c>
-      <c r="E102" s="60"/>
-      <c r="F102" s="61"/>
-    </row>
-    <row r="103" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A103" s="3" t="s">
+      <c r="E119" s="85"/>
+      <c r="F119" s="86"/>
+    </row>
+    <row r="120" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A120" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B103" s="13"/>
-      <c r="C103" s="19"/>
-      <c r="D103" s="43"/>
-      <c r="E103" s="44"/>
-      <c r="F103" s="45"/>
-    </row>
-    <row r="104" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A104" s="3" t="s">
+      <c r="B120" s="13"/>
+      <c r="C120" s="19"/>
+      <c r="D120" s="70"/>
+      <c r="E120" s="71"/>
+      <c r="F120" s="72"/>
+    </row>
+    <row r="121" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A121" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B104" s="13"/>
-      <c r="C104" s="14"/>
-      <c r="D104" s="46"/>
-      <c r="E104" s="46"/>
-      <c r="F104" s="47"/>
-    </row>
-    <row r="105" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A105" s="15" t="s">
+      <c r="B121" s="13"/>
+      <c r="C121" s="14"/>
+      <c r="D121" s="73"/>
+      <c r="E121" s="73"/>
+      <c r="F121" s="74"/>
+    </row>
+    <row r="122" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A122" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="B105" s="16"/>
-      <c r="C105" s="20"/>
-      <c r="D105" s="48" t="s">
+      <c r="B122" s="16"/>
+      <c r="C122" s="20"/>
+      <c r="D122" s="75" t="s">
         <v>15</v>
       </c>
-      <c r="E105" s="48"/>
-      <c r="F105" s="49"/>
-      <c r="G105" s="35" t="s">
+      <c r="E122" s="75"/>
+      <c r="F122" s="76"/>
+      <c r="G122" s="35" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A106" s="6"/>
-      <c r="B106" s="17"/>
-      <c r="C106" s="18"/>
-      <c r="D106" s="17"/>
-      <c r="E106" s="17"/>
-      <c r="F106" s="18"/>
-      <c r="G106" s="35" t="s">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A123" s="6"/>
+      <c r="B123" s="17"/>
+      <c r="C123" s="18"/>
+      <c r="D123" s="17"/>
+      <c r="E123" s="17"/>
+      <c r="F123" s="18"/>
+      <c r="G123" s="35" t="s">
         <v>24</v>
       </c>
     </row>
@@ -2245,29 +2447,29 @@
     <sortCondition ref="K6:K93"/>
   </sortState>
   <mergeCells count="23">
+    <mergeCell ref="D120:F120"/>
+    <mergeCell ref="D121:F121"/>
+    <mergeCell ref="D122:F122"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="D116:E116"/>
+    <mergeCell ref="A118:F118"/>
+    <mergeCell ref="A119:C119"/>
+    <mergeCell ref="D119:F119"/>
+    <mergeCell ref="E7:E8"/>
+    <mergeCell ref="A117:B117"/>
+    <mergeCell ref="C117:F117"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="D4:F4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="E5:F5"/>
     <mergeCell ref="E6:F6"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="A7:A8"/>
     <mergeCell ref="B7:B8"/>
     <mergeCell ref="C7:C8"/>
     <mergeCell ref="D7:D8"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="D4:F4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="D103:F103"/>
-    <mergeCell ref="D104:F104"/>
-    <mergeCell ref="D105:F105"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="D99:E99"/>
-    <mergeCell ref="A101:F101"/>
-    <mergeCell ref="A102:C102"/>
-    <mergeCell ref="D102:F102"/>
-    <mergeCell ref="E7:E8"/>
-    <mergeCell ref="A100:B100"/>
-    <mergeCell ref="C100:F100"/>
   </mergeCells>
   <pageMargins left="0.70866141732283461" right="0.51181102362204722" top="0.74803149606299213" bottom="1.7716535433070866" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="93" fitToHeight="0" orientation="portrait" r:id="rId1"/>
